--- a/JsonConverter/ExcelFiles/Cocktail.xlsx
+++ b/JsonConverter/ExcelFiles/Cocktail.xlsx
@@ -14,75 +14,162 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="23">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="52">
+  <x:si>
+    <x:t>Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_ZenStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판촉용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>씀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시큼함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달콤함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SparkleStar_1</x:t>
+  </x:si>
   <x:si>
     <x:t>Cocktail_BlueFairy_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_SparkleStar_1</x:t>
+    <x:t>Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거품많음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극적</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급스러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FromType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TasteType</x:t>
   </x:si>
   <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
     <x:t>IconPath</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TasteType</x:t>
+    <x:t>거트 펀치</x:t>
   </x:si>
   <x:si>
     <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
   </x:si>
   <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Brandtini_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달콤함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FromType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급스러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬</x:t>
+    <x:t>Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -314,6 +401,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -396,6 +484,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -430,6 +519,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -474,6 +564,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -517,6 +608,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -601,6 +693,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -621,6 +714,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -651,6 +745,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1365,70 +1460,70 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>41</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>12</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G2" s="1"/>
       <x:c r="H2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>2</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
-        <x:v>8</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>4</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="G3" s="13"/>
       <x:c r="H3" s="13"/>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>22</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C4" s="3"/>
       <x:c r="D4" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F4" s="4"/>
       <x:c r="G4" s="4"/>
@@ -1441,17 +1536,17 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>1</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C5" s="5"/>
       <x:c r="D5" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F5" s="4"/>
       <x:c r="G5" s="4"/>
@@ -1464,17 +1559,17 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>0</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C6" s="5"/>
       <x:c r="D6" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="F6" s="4"/>
       <x:c r="G6" s="4"/>
@@ -1486,17 +1581,17 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>13</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C7" s="3"/>
       <x:c r="D7" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="4"/>
@@ -1509,17 +1604,17 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>19</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="3"/>
       <x:c r="D8" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
@@ -1531,11 +1626,19 @@
       <x:c r="M8" s="4"/>
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A9" s="6"/>
-      <x:c r="B9" s="3"/>
+      <x:c r="A9" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="C9" s="3"/>
-      <x:c r="D9" s="4"/>
-      <x:c r="E9" s="4"/>
+      <x:c r="D9" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="F9" s="4"/>
       <x:c r="G9" s="4"/>
       <x:c r="H9" s="4"/>
@@ -1546,11 +1649,19 @@
       <x:c r="M9" s="4"/>
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A10" s="1"/>
-      <x:c r="B10" s="1"/>
+      <x:c r="A10" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>5</x:v>
+      </x:c>
       <x:c r="C10" s="1"/>
-      <x:c r="D10" s="4"/>
-      <x:c r="E10" s="4"/>
+      <x:c r="D10" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E10" s="4" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="F10" s="4"/>
       <x:c r="G10" s="4"/>
       <x:c r="H10" s="4"/>
@@ -1561,11 +1672,19 @@
       <x:c r="M10" s="4"/>
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A11" s="1"/>
-      <x:c r="B11" s="1"/>
+      <x:c r="A11" s="6" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B11" s="6" t="s">
+        <x:v>10</x:v>
+      </x:c>
       <x:c r="C11" s="1"/>
-      <x:c r="D11" s="4"/>
-      <x:c r="E11" s="4"/>
+      <x:c r="D11" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E11" s="4" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="F11" s="4"/>
       <x:c r="G11" s="4"/>
       <x:c r="H11" s="4"/>
@@ -1576,11 +1695,19 @@
       <x:c r="M11" s="4"/>
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A12" s="6"/>
-      <x:c r="B12" s="6"/>
+      <x:c r="A12" s="6" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B12" s="6" t="s">
+        <x:v>46</x:v>
+      </x:c>
       <x:c r="C12" s="6"/>
-      <x:c r="D12" s="4"/>
-      <x:c r="E12" s="4"/>
+      <x:c r="D12" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E12" s="4" t="s">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="F12" s="4"/>
       <x:c r="G12" s="4"/>
       <x:c r="H12" s="4"/>
@@ -1591,11 +1718,19 @@
       <x:c r="M12" s="4"/>
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A13" s="3"/>
-      <x:c r="B13" s="3"/>
+      <x:c r="A13" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
       <x:c r="C13" s="3"/>
-      <x:c r="D13" s="4"/>
-      <x:c r="E13" s="4"/>
+      <x:c r="D13" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E13" s="4" t="s">
+        <x:v>31</x:v>
+      </x:c>
       <x:c r="F13" s="4"/>
       <x:c r="G13" s="4"/>
       <x:c r="H13" s="4"/>
@@ -1606,11 +1741,19 @@
       <x:c r="M13" s="4"/>
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A14" s="1"/>
-      <x:c r="B14" s="1"/>
+      <x:c r="A14" s="6" t="s">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="B14" s="7" t="s">
+        <x:v>19</x:v>
+      </x:c>
       <x:c r="C14" s="1"/>
-      <x:c r="D14" s="4"/>
-      <x:c r="E14" s="4"/>
+      <x:c r="D14" s="4" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="E14" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="F14" s="4"/>
       <x:c r="G14" s="4"/>
       <x:c r="H14" s="4"/>
@@ -1621,11 +1764,19 @@
       <x:c r="M14" s="4"/>
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
-      <x:c r="A15" s="1"/>
-      <x:c r="B15" s="1"/>
+      <x:c r="A15" s="6" t="s">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
       <x:c r="C15" s="1"/>
-      <x:c r="D15" s="4"/>
-      <x:c r="E15" s="4"/>
+      <x:c r="D15" s="4" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="E15" s="4" t="s">
+        <x:v>6</x:v>
+      </x:c>
       <x:c r="F15" s="4"/>
       <x:c r="G15" s="4"/>
       <x:c r="H15" s="4"/>
@@ -1635,93 +1786,133 @@
       <x:c r="L15" s="4"/>
       <x:c r="M15" s="4"/>
     </x:row>
-    <x:row r="16" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A16" s="7"/>
-      <x:c r="B16" s="7"/>
+    <x:row r="16" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A16" s="6" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B16" s="7" t="s">
+        <x:v>9</x:v>
+      </x:c>
       <x:c r="C16" s="7"/>
-    </x:row>
-    <x:row r="17" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A17" s="8"/>
-      <x:c r="B17" s="8"/>
+      <x:c r="D16" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E16" s="2" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A17" s="6" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B17" s="8" t="s">
+        <x:v>47</x:v>
+      </x:c>
       <x:c r="C17" s="8"/>
-    </x:row>
-    <x:row r="18" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A18" s="8"/>
-      <x:c r="B18" s="8"/>
+      <x:c r="D17" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E17" s="2" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A18" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B18" s="8" t="s">
+        <x:v>48</x:v>
+      </x:c>
       <x:c r="C18" s="8"/>
-    </x:row>
-    <x:row r="19" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A19" s="8"/>
-      <x:c r="B19" s="8"/>
+      <x:c r="D18" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E18" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
+      <x:c r="A19" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="B19" s="8" t="s">
+        <x:v>49</x:v>
+      </x:c>
       <x:c r="C19" s="8"/>
+      <x:c r="D19" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="E19" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="8"/>
+      <x:c r="A20" s="6"/>
       <x:c r="B20" s="8"/>
       <x:c r="C20" s="8"/>
     </x:row>
     <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A21" s="8"/>
+      <x:c r="A21" s="6"/>
       <x:c r="B21" s="8"/>
       <x:c r="C21" s="8"/>
     </x:row>
     <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A22" s="8"/>
+      <x:c r="A22" s="6"/>
       <x:c r="B22" s="8"/>
       <x:c r="C22" s="8"/>
     </x:row>
     <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A23" s="8"/>
+      <x:c r="A23" s="6"/>
       <x:c r="B23" s="8"/>
       <x:c r="C23" s="8"/>
     </x:row>
     <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A24" s="8"/>
+      <x:c r="A24" s="6"/>
       <x:c r="B24" s="8"/>
       <x:c r="C24" s="8"/>
     </x:row>
     <x:row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A25" s="8"/>
+      <x:c r="A25" s="6"/>
       <x:c r="B25" s="8"/>
       <x:c r="C25" s="8"/>
     </x:row>
     <x:row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A26" s="9"/>
+      <x:c r="A26" s="6"/>
       <x:c r="B26" s="9"/>
       <x:c r="C26" s="9"/>
     </x:row>
     <x:row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A27" s="9"/>
+      <x:c r="A27" s="6"/>
       <x:c r="B27" s="9"/>
       <x:c r="C27" s="9"/>
     </x:row>
     <x:row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A28" s="9"/>
+      <x:c r="A28" s="6"/>
       <x:c r="B28" s="9"/>
       <x:c r="C28" s="9"/>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A29" s="9"/>
+      <x:c r="A29" s="6"/>
       <x:c r="B29" s="9"/>
       <x:c r="C29" s="9"/>
     </x:row>
     <x:row r="30" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A30" s="9"/>
+      <x:c r="A30" s="6"/>
       <x:c r="B30" s="9"/>
       <x:c r="C30" s="9"/>
     </x:row>
     <x:row r="31" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A31" s="9"/>
+      <x:c r="A31" s="6"/>
       <x:c r="B31" s="9"/>
       <x:c r="C31" s="9"/>
     </x:row>
     <x:row r="32" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A32" s="10"/>
+      <x:c r="A32" s="6"/>
       <x:c r="B32" s="10"/>
       <x:c r="C32" s="10"/>
     </x:row>
     <x:row r="33" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A33" s="10"/>
+      <x:c r="A33" s="6"/>
       <x:c r="B33" s="10"/>
       <x:c r="C33" s="10"/>
     </x:row>

--- a/JsonConverter/ExcelFiles/Cocktail.xlsx
+++ b/JsonConverter/ExcelFiles/Cocktail.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="20310" windowHeight="11070"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="14445" windowHeight="7935"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -16,157 +16,157 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="52">
   <x:si>
+    <x:t>Cocktail_SparkleStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_FluffyDream_1</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_ZenStar_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CobaltVelvet_1</x:t>
+    <x:t>Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판촉용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FromType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TasteType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거품 많은 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극적인 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쓴 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급스러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달콤한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시큼한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:t>파일 드라이버</x:t>
   </x:si>
   <x:si>
-    <x:t>판촉용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>씀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시큼함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주</x:t>
+    <x:t>브랜티니</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
   </x:si>
   <x:si>
     <x:t>수플렉스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달콤함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SparkleStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BlueFairy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Brandtini_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Piledriver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GutPunch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Suplex_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거품많음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FrothyWater_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극적</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급스러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FromType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TasteType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식</x:t>
   </x:si>
   <x:si>
     <x:t>배드 터치</x:t>
@@ -1460,67 +1460,67 @@
   <x:sheetData>
     <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="G2" s="1"/>
       <x:c r="H2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>11</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>34</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>38</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
-        <x:v>37</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>35</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>39</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="G3" s="13"/>
       <x:c r="H3" s="13"/>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C4" s="3"/>
       <x:c r="D4" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
         <x:v>30</x:v>
@@ -1536,14 +1536,14 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>26</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="C5" s="5"/>
       <x:c r="D5" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
         <x:v>30</x:v>
@@ -1559,14 +1559,14 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C6" s="5"/>
       <x:c r="D6" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
         <x:v>30</x:v>
@@ -1581,17 +1581,17 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>25</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C7" s="3"/>
       <x:c r="D7" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F7" s="4"/>
       <x:c r="G7" s="4"/>
@@ -1604,17 +1604,17 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C8" s="3"/>
       <x:c r="D8" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F8" s="4"/>
       <x:c r="G8" s="4"/>
@@ -1627,17 +1627,17 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>20</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
       <x:c r="C9" s="3"/>
       <x:c r="D9" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F9" s="4"/>
       <x:c r="G9" s="4"/>
@@ -1650,17 +1650,17 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="C10" s="1"/>
       <x:c r="D10" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F10" s="4"/>
       <x:c r="G10" s="4"/>
@@ -1673,17 +1673,17 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C11" s="1"/>
       <x:c r="D11" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F11" s="4"/>
       <x:c r="G11" s="4"/>
@@ -1696,14 +1696,14 @@
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>0</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C12" s="6"/>
       <x:c r="D12" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
         <x:v>30</x:v>
@@ -1719,17 +1719,17 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>43</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
       <x:c r="C13" s="3"/>
       <x:c r="D13" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="F13" s="4"/>
       <x:c r="G13" s="4"/>
@@ -1742,17 +1742,17 @@
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>19</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="C14" s="1"/>
       <x:c r="D14" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E14" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F14" s="4"/>
       <x:c r="G14" s="4"/>
@@ -1765,17 +1765,17 @@
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C15" s="1"/>
       <x:c r="D15" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F15" s="4"/>
       <x:c r="G15" s="4"/>
@@ -1788,62 +1788,62 @@
     </x:row>
     <x:row r="16" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>9</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C16" s="7"/>
       <x:c r="D16" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B17" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C17" s="8"/>
       <x:c r="D17" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>50</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B18" s="8" t="s">
-        <x:v>48</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C18" s="8"/>
       <x:c r="D18" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B19" s="8" t="s">
-        <x:v>49</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C19" s="8"/>
       <x:c r="D19" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Cocktail.xlsx
+++ b/JsonConverter/ExcelFiles/Cocktail.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="14445" windowHeight="7935"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="20055" windowHeight="10080"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -14,72 +14,240 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="52">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="86">
+  <x:si>
+    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_ZenStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SugarRush_1</x:t>
+  </x:si>
   <x:si>
     <x:t>Cocktail_SparkleStar_1</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_PianoWoman_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_Brandtini_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BlueFairy_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocktail_FrothyWater_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_Piledriver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CobaltVelvet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FluffyDream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GutPunch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_ZenStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Suplex_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Beer_1</x:t>
+    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달콤한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급스러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시큼한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쓴 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MakeRecipe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판촉용</x:t>
   </x:si>
   <x:si>
     <x:t>젠스타</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판촉용</x:t>
-  </x:si>
-  <x:si>
     <x:t>클래식</x:t>
   </x:si>
   <x:si>
-    <x:t>맥주</x:t>
+    <x:t>제조법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬는 아델하이드 2, 델타가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타는 아델하이드 2, 델타가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극적인 드링크</x:t>
   </x:si>
   <x:si>
     <x:t>FromType</x:t>
@@ -94,82 +262,16 @@
     <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극적인 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쓴 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급스러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달콤한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시큼한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치</x:t>
+    <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -401,7 +503,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -484,7 +585,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -519,7 +619,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -564,7 +663,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -608,7 +706,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -693,7 +790,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -714,7 +810,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -745,7 +840,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1458,57 +1552,64 @@
     <x:col min="9" max="16384" width="12.5703125" style="2"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:3" ht="15.75" customHeight="1">
+    <x:row r="1" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="D1" s="2" t="s">
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="G2" s="1"/>
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="G2" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
       <x:c r="H2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>42</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>26</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
-        <x:v>23</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>22</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="G3" s="13"/>
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>76</x:v>
+      </x:c>
       <x:c r="H3" s="13"/>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
@@ -1516,16 +1617,20 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="C4" s="3"/>
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>58</x:v>
+      </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F4" s="4"/>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F4" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="G4" s="4"/>
       <x:c r="H4" s="4"/>
       <x:c r="I4" s="4"/>
@@ -1536,19 +1641,23 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="C5" s="5"/>
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C5" s="5" t="s">
+        <x:v>59</x:v>
+      </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F5" s="4"/>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F5" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="G5" s="4"/>
       <x:c r="H5" s="4"/>
       <x:c r="I5" s="4"/>
@@ -1559,19 +1668,23 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>4</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>48</x:v>
-      </x:c>
-      <x:c r="C6" s="5"/>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
+        <x:v>85</x:v>
+      </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F6" s="4"/>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F6" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="G6" s="4"/>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="4"/>
@@ -1581,19 +1694,23 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>47</x:v>
-      </x:c>
-      <x:c r="C7" s="3"/>
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="C7" s="3" t="s">
+        <x:v>67</x:v>
+      </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F7" s="4"/>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F7" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
       <x:c r="G7" s="4"/>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="4"/>
@@ -1604,19 +1721,23 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C8" s="3"/>
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
+        <x:v>64</x:v>
+      </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F8" s="4"/>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="F8" s="4" t="s">
+        <x:v>51</x:v>
+      </x:c>
       <x:c r="G8" s="4"/>
       <x:c r="H8" s="4"/>
       <x:c r="I8" s="4"/>
@@ -1627,19 +1748,23 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="C9" s="3"/>
-      <x:c r="D9" s="4" t="s">
-        <x:v>31</x:v>
-      </x:c>
-      <x:c r="E9" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F9" s="4"/>
       <x:c r="G9" s="4"/>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="4"/>
@@ -1650,19 +1775,23 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
-      <x:c r="C10" s="1"/>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F10" s="4"/>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F10" s="4" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="G10" s="4"/>
       <x:c r="H10" s="4"/>
       <x:c r="I10" s="4"/>
@@ -1673,19 +1802,23 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>13</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="C11" s="1"/>
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>44</x:v>
-      </x:c>
-      <x:c r="F11" s="4"/>
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="F11" s="4" t="s">
+        <x:v>40</x:v>
+      </x:c>
       <x:c r="G11" s="4"/>
       <x:c r="H11" s="4"/>
       <x:c r="I11" s="4"/>
@@ -1696,19 +1829,23 @@
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C12" s="6"/>
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C12" s="6" t="s">
+        <x:v>73</x:v>
+      </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="F12" s="4"/>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F12" s="4" t="s">
+        <x:v>27</x:v>
+      </x:c>
       <x:c r="G12" s="4"/>
       <x:c r="H12" s="4"/>
       <x:c r="I12" s="4"/>
@@ -1719,19 +1856,23 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="C13" s="3"/>
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="F13" s="4"/>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F13" s="4" t="s">
+        <x:v>28</x:v>
+      </x:c>
       <x:c r="G13" s="4"/>
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="4"/>
@@ -1742,19 +1883,23 @@
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C14" s="1"/>
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E14" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F14" s="4"/>
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="s">
+        <x:v>51</x:v>
+      </x:c>
       <x:c r="G14" s="4"/>
       <x:c r="H14" s="4"/>
       <x:c r="I14" s="4"/>
@@ -1765,19 +1910,23 @@
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C15" s="1"/>
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="F15" s="4"/>
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="F15" s="4" t="s">
+        <x:v>51</x:v>
+      </x:c>
       <x:c r="G15" s="4"/>
       <x:c r="H15" s="4"/>
       <x:c r="I15" s="4"/>
@@ -1786,64 +1935,84 @@
       <x:c r="L15" s="4"/>
       <x:c r="M15" s="4"/>
     </x:row>
-    <x:row r="16" spans="1:5" ht="15.75" customHeight="1">
+    <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C16" s="7"/>
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C16" s="7" t="s">
+        <x:v>63</x:v>
+      </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F16" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
+      <x:c r="A17" s="6" t="s">
         <x:v>20</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17" spans="1:5" ht="15.75" customHeight="1">
-      <x:c r="A17" s="6" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="B17" s="8" t="s">
-        <x:v>33</x:v>
-      </x:c>
-      <x:c r="C17" s="8"/>
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="C17" s="8" t="s">
+        <x:v>56</x:v>
+      </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>20</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:5" ht="15.75" customHeight="1">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F17" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B18" s="8" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C18" s="8"/>
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C18" s="8" t="s">
+        <x:v>74</x:v>
+      </x:c>
       <x:c r="D18" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:5" ht="15.75" customHeight="1">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F18" s="2" t="s">
+        <x:v>28</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B19" s="8" t="s">
-        <x:v>35</x:v>
-      </x:c>
-      <x:c r="C19" s="8"/>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C19" s="8" t="s">
+        <x:v>48</x:v>
+      </x:c>
       <x:c r="D19" s="2" t="s">
-        <x:v>24</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>36</x:v>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F19" s="2" t="s">
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Cocktail.xlsx
+++ b/JsonConverter/ExcelFiles/Cocktail.xlsx
@@ -16,262 +16,262 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="86">
   <x:si>
+    <x:t>Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_ZenStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SparkleStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MakeRecipe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극적인 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FromType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거품 많은 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TasteType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판촉용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제조법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시큼한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쓴 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달콤한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급스러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
     <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
   </x:si>
   <x:si>
-    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
     <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_GutPunch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_ZenStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Suplex_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SparkleStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BlueFairy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Piledriver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Brandtini_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FluffyDream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CobaltVelvet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FrothyWater_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달콤한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급스러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시큼한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쓴 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
+    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
   </x:si>
   <x:si>
     <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
   </x:si>
   <x:si>
-    <x:t>MakeRecipe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판촉용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제조법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬는 아델하이드 2, 델타가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
+    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
   </x:si>
   <x:si>
     <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
   </x:si>
   <x:si>
-    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타는 아델하이드 2, 델타가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극적인 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FromType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TasteType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거품 많은 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
     <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
   </x:si>
   <x:si>
-    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
+    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -503,6 +503,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -585,6 +586,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -619,6 +621,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -663,6 +666,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -706,6 +710,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -790,6 +795,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -810,6 +816,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -840,6 +847,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1554,82 +1562,82 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>9</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H2" s="1"/>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>49</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>75</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
-        <x:v>47</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>79</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>78</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>76</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="H3" s="13"/>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="C4" s="3" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="C4" s="3" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="D4" s="4" t="s">
+      <x:c r="F4" s="4" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F4" s="4" t="s">
-        <x:v>27</x:v>
       </x:c>
       <x:c r="G4" s="4"/>
       <x:c r="H4" s="4"/>
@@ -1641,22 +1649,22 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>11</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>59</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>70</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F5" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G5" s="4"/>
       <x:c r="H5" s="4"/>
@@ -1668,22 +1676,22 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>13</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C6" s="5" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D6" s="4" t="s">
         <x:v>35</x:v>
       </x:c>
-      <x:c r="C6" s="5" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="D6" s="4" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F6" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G6" s="4"/>
       <x:c r="H6" s="4"/>
@@ -1694,22 +1702,22 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>42</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>67</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>3</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="F7" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G7" s="4"/>
       <x:c r="H7" s="4"/>
@@ -1721,22 +1729,22 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="E8" s="4" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="F8" s="4" t="s">
         <x:v>29</x:v>
-      </x:c>
-      <x:c r="C8" s="3" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D8" s="4" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="E8" s="4" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="F8" s="4" t="s">
-        <x:v>51</x:v>
       </x:c>
       <x:c r="G8" s="4"/>
       <x:c r="H8" s="4"/>
@@ -1748,22 +1756,22 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>69</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F9" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G9" s="4"/>
       <x:c r="H9" s="4"/>
@@ -1775,22 +1783,22 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>1</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F10" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G10" s="4"/>
       <x:c r="H10" s="4"/>
@@ -1802,22 +1810,22 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>33</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="F11" s="4" t="s">
-        <x:v>40</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="G11" s="4"/>
       <x:c r="H11" s="4"/>
@@ -1829,22 +1837,22 @@
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>17</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F12" s="4" t="s">
-        <x:v>27</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="G12" s="4"/>
       <x:c r="H12" s="4"/>
@@ -1856,22 +1864,22 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>0</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F13" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G13" s="4"/>
       <x:c r="H13" s="4"/>
@@ -1883,22 +1891,22 @@
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>5</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>52</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E14" s="4" t="s">
-        <x:v>31</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="F14" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G14" s="4"/>
       <x:c r="H14" s="4"/>
@@ -1910,22 +1918,22 @@
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="D15" s="4" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="E15" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F15" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="G15" s="4"/>
       <x:c r="H15" s="4"/>
@@ -1937,82 +1945,82 @@
     </x:row>
     <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>50</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C16" s="7" t="s">
-        <x:v>63</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F16" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B17" s="8" t="s">
-        <x:v>30</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C17" s="8" t="s">
-        <x:v>56</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F17" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>18</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B18" s="8" t="s">
-        <x:v>25</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C18" s="8" t="s">
-        <x:v>74</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F18" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B19" s="8" t="s">
-        <x:v>23</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C19" s="8" t="s">
-        <x:v>48</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="F19" s="2" t="s">
-        <x:v>28</x:v>
+        <x:v>55</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Cocktail.xlsx
+++ b/JsonConverter/ExcelFiles/Cocktail.xlsx
@@ -14,264 +14,285 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="86">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="93">
+  <x:si>
+    <x:t>유서 깊음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단순함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoodType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화끈함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SparkleStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판촉용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제조법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_ZenStar_1</x:t>
+  </x:si>
   <x:si>
     <x:t>Cocktail_GutPunch_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_ZenStar_1</x:t>
+    <x:t>Cocktail_Suplex_1</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_BadTouch_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_Suplex_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SparkleStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Piledriver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Brandtini_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FluffyDream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FrothyWater_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CobaltVelvet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BlueFairy_1</x:t>
+    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쓴 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달콤한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시큼한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급스러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극적인 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
   </x:si>
   <x:si>
     <x:t>MakeRecipe</x:t>
   </x:si>
   <x:si>
+    <x:t>거품 많은 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TasteType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FromType</x:t>
+  </x:si>
+  <x:si>
     <x:t>Description</x:t>
   </x:si>
   <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극적인 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FromType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거품 많은 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TasteType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판촉용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제조법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시큼한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쓴 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달콤한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급스러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
-  </x:si>
-  <x:si>
     <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
   </x:si>
   <x:si>
-    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
+    <x:t>행복함</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -503,7 +524,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -586,7 +606,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -621,7 +640,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -666,7 +684,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -710,7 +727,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -795,7 +811,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -816,7 +831,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -847,7 +861,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1562,84 +1575,90 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>31</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="H2" s="1"/>
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H2" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>34</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>51</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>17</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
-        <x:v>16</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>22</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>20</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="H3" s="13"/>
+        <x:v>3</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="s">
+        <x:v>88</x:v>
+      </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>12</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>53</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>83</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F4" s="4" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G4" s="4"/>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G4" s="4" t="s">
+        <x:v>92</x:v>
+      </x:c>
       <x:c r="H4" s="4"/>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1649,24 +1668,26 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>4</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>42</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>81</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F5" s="4" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G5" s="4"/>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G5" s="4" t="s">
+        <x:v>92</x:v>
+      </x:c>
       <x:c r="H5" s="4"/>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1676,24 +1697,26 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>15</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>50</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F6" s="4" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G6" s="4"/>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G6" s="4" t="s">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1702,24 +1725,26 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>63</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F7" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G7" s="4"/>
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G7" s="4" t="s">
+        <x:v>92</x:v>
+      </x:c>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1729,24 +1754,26 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>70</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="F8" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G8" s="4"/>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G8" s="4" t="s">
+        <x:v>92</x:v>
+      </x:c>
       <x:c r="H8" s="4"/>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1756,24 +1783,26 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="C9" s="3" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="D9" s="4" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="E9" s="4" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="F9" s="4" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G9" s="4" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="C9" s="3" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="D9" s="4" t="s">
-        <x:v>36</x:v>
-      </x:c>
-      <x:c r="E9" s="4" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="F9" s="4" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G9" s="4"/>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
@@ -1786,21 +1815,23 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="E10" s="4" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E10" s="4" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="F10" s="4" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G10" s="4"/>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G10" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="H10" s="4"/>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
@@ -1810,24 +1841,26 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>40</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F11" s="4" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="G11" s="4"/>
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="G11" s="4" t="s">
+        <x:v>4</x:v>
+      </x:c>
       <x:c r="H11" s="4"/>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
@@ -1840,21 +1873,23 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>39</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>75</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F12" s="4" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G12" s="4"/>
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="G12" s="4" t="s">
+        <x:v>2</x:v>
+      </x:c>
       <x:c r="H12" s="4"/>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>
@@ -1864,24 +1899,26 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F13" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="G13" s="4"/>
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G13" s="4" t="s">
+        <x:v>0</x:v>
+      </x:c>
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="4"/>
       <x:c r="J13" s="4"/>
@@ -1891,24 +1928,26 @@
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B14" s="7" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E14" s="4" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G14" s="4" t="s">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="B14" s="7" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D14" s="4" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="E14" s="4" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="F14" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G14" s="4"/>
       <x:c r="H14" s="4"/>
       <x:c r="I14" s="4"/>
       <x:c r="J14" s="4"/>
@@ -1918,24 +1957,26 @@
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F15" s="4" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="G15" s="4"/>
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="G15" s="4" t="s">
+        <x:v>1</x:v>
+      </x:c>
       <x:c r="H15" s="4"/>
       <x:c r="I15" s="4"/>
       <x:c r="J15" s="4"/>
@@ -1943,84 +1984,96 @@
       <x:c r="L15" s="4"/>
       <x:c r="M15" s="4"/>
     </x:row>
-    <x:row r="16" spans="1:6" ht="15.75" customHeight="1">
+    <x:row r="16" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>32</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C16" s="7" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D16" s="2" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E16" s="2" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F16" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G16" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A17" s="6" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B17" s="8" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="C17" s="8" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="D17" s="2" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E17" s="2" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F17" s="2" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="G17" s="2" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A18" s="6" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="B18" s="8" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="C18" s="8" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D18" s="2" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="E18" s="2" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="F18" s="2" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D16" s="2" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="E16" s="2" t="s">
+      <x:c r="G18" s="2" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A19" s="6" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B19" s="8" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="C19" s="8" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="F16" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A17" s="6" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B17" s="8" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="C17" s="8" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D17" s="2" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E17" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F17" s="2" t="s">
-        <x:v>33</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A18" s="6" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B18" s="8" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="C18" s="8" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D18" s="2" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E18" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="F18" s="2" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:6" ht="15.75" customHeight="1">
-      <x:c r="A19" s="6" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="B19" s="8" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="C19" s="8" t="s">
-        <x:v>26</x:v>
-      </x:c>
       <x:c r="D19" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="F19" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G19" s="2" t="s">
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:3" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Cocktail.xlsx
+++ b/JsonConverter/ExcelFiles/Cocktail.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="20055" windowHeight="10080"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="24465" windowHeight="11745"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -14,12 +14,210 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="93">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="126">
+  <x:si>
+    <x:t>거품 많은 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FromType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MakeRecipe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션샤인 클라우드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머큐리 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 맨은 아델하이드 2, 브론순 추출액 3, 델타 가루 5, 플래너자이드 5, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인은 브론순 추출액 1, 델타 가루 3, 플래너자이드 3 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 맨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그리즐리 템플</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SunshineCloud_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머큐리 블라스트는 아델하이드 1, 브론순 추출액 1, 델타 가루 3, 플래너자이드 3, 카모트린 2 전부넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 한잔이면 충분히 그 행성처럼 얼굴이 붉게 된다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화끈함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행복함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>각성용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단순함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판촉용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제조법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달콤한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시큼한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쓴 드링크</x:t>
+  </x:si>
   <x:si>
     <x:t>유서 깊음</x:t>
   </x:si>
   <x:si>
-    <x:t>단순함</x:t>
+    <x:t>고급스러움</x:t>
   </x:si>
   <x:si>
     <x:t>부드러움</x:t>
@@ -28,271 +226,172 @@
     <x:t>MoodType</x:t>
   </x:si>
   <x:si>
-    <x:t>화끈함</x:t>
+    <x:t>Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_ZenStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoMan_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술을 제작하면서 어ᄄᅠᆫ 온도계도 피해입지 않았음을 알려드리는 바입니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"매달마다 1주일씩 관찰할 수 있는 월면 강입자포와는 아무런 연관이 없습니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이걸 마시면 자네가 술이 깨던가 차가움에 머리가 깨지던가, 둘 중 하나일 거야."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술이 쓰였던 영화의 팬이 아니라면, 이 술을 참기는 힘들것입니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술은 술집 피아니스트 연맹 또는 구성원들의 의견을 대변하지 않습니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"거울 앞에 서서 블리딩 제인을 세 번 불러봐, 그럼 바보처럼 보일꺼야."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그리즐리 템플은 아델하이드 3, 브론순 추출액 3, 델타 가루 3, 카모트린 1 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"맛이 오래된 초콜릿 우유 같고 냄새도 꼭 그래. 어ᄄᅠᆫ 사람은 맛이 카라멜 캍다고 하기도 하고..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트는 브론순 추출액 6, 델타 가루 1, 플래너자이드 4, 카모트린 2 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션샤인 클라우드는 아델하이드 2, 브론순 추출액 2, 카모트린 추가 가능 전부 넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문블라스트는 아델하이드 6, 델타가루 1, 플래너자이드 1, 카모트린 2 전부 넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크는 델타 가루 2, 플래너자이드 4, 카모트린 추가 가능, 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극적인 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TasteType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Beer_1</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_Piledriver_1</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Mercryblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_CobaltVelvet_1</x:t>
   </x:si>
   <x:si>
+    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_FluffyDream_1</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocktail_CreviceSpike_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BleedingJane_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SparkleStar_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_FrothyWater_1</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_BlueFairy_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_Brandtini_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SparkleStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판촉용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제조법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_ZenStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GutPunch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Suplex_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쓴 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달콤한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시큼한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급스러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극적인 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MakeRecipe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거품 많은 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TasteType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FromType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행복함</x:t>
+    <x:t>Cocktail_MoonBlast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Mercuryblast_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1567,7 +1666,7 @@
     <x:col min="1" max="1" width="19.42578125" style="2" customWidth="1"/>
     <x:col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="50.7109375" style="2" customWidth="1"/>
-    <x:col min="4" max="4" width="26.5703125" style="2" customWidth="1"/>
+    <x:col min="4" max="4" width="89" style="2" customWidth="1"/>
     <x:col min="5" max="7" width="12.5703125" style="2"/>
     <x:col min="8" max="8" width="28.42578125" style="2" customWidth="1"/>
     <x:col min="9" max="16384" width="12.5703125" style="2"/>
@@ -1575,89 +1674,89 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>22</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>33</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>25</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>72</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>90</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
-        <x:v>85</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>87</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>89</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>3</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>88</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>15</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>79</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>41</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="F4" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G4" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H4" s="4"/>
       <x:c r="I4" s="4"/>
@@ -1668,25 +1767,25 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>16</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>69</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>58</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>49</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="F5" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G5" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H5" s="4"/>
       <x:c r="I5" s="4"/>
@@ -1697,25 +1796,25 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>9</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>78</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>55</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="F6" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G6" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H6" s="4"/>
       <x:c r="I6" s="4"/>
@@ -1725,25 +1824,25 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>81</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>45</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="F7" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H7" s="4"/>
       <x:c r="I7" s="4"/>
@@ -1754,25 +1853,25 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B8" s="3" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="C8" s="3" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D8" s="4" t="s">
         <x:v>12</x:v>
-      </x:c>
-      <x:c r="B8" s="3" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="C8" s="3" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="D8" s="4" t="s">
-        <x:v>35</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
         <x:v>61</x:v>
       </x:c>
       <x:c r="F8" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G8" s="4" t="s">
-        <x:v>92</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H8" s="4"/>
       <x:c r="I8" s="4"/>
@@ -1783,25 +1882,25 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>46</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F9" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G9" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H9" s="4"/>
       <x:c r="I9" s="4"/>
@@ -1812,25 +1911,25 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="E10" s="4" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F10" s="4" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="D10" s="4" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="E10" s="4" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="F10" s="4" t="s">
-        <x:v>74</x:v>
-      </x:c>
       <x:c r="G10" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H10" s="4"/>
       <x:c r="I10" s="4"/>
@@ -1841,25 +1940,25 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>68</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="F11" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G11" s="4" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="4"/>
       <x:c r="I11" s="4"/>
@@ -1870,25 +1969,25 @@
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>7</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>42</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F12" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G12" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="H12" s="4"/>
       <x:c r="I12" s="4"/>
@@ -1899,25 +1998,25 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>14</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="F13" s="4" t="s">
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G13" s="4" t="s">
-        <x:v>0</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H13" s="4"/>
       <x:c r="I13" s="4"/>
@@ -1928,25 +2027,25 @@
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>27</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E14" s="4" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G14" s="4" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="D14" s="4" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="E14" s="4" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F14" s="4" t="s">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="G14" s="4" t="s">
-        <x:v>1</x:v>
       </x:c>
       <x:c r="H14" s="4"/>
       <x:c r="I14" s="4"/>
@@ -1957,25 +2056,25 @@
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="F15" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G15" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="H15" s="4"/>
       <x:c r="I15" s="4"/>
@@ -1986,135 +2085,279 @@
     </x:row>
     <x:row r="16" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>28</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="C16" s="7" t="s">
-        <x:v>53</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F16" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G16" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="B17" s="8" t="s">
-        <x:v>82</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C17" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="2" t="s">
-        <x:v>26</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>1</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>6</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="B18" s="8" t="s">
-        <x:v>70</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C18" s="8" t="s">
-        <x:v>18</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="F18" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:7" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B19" s="8" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="C19" s="8" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D19" s="2" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E19" s="2" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="F19" s="2" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G19" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A20" s="6" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="B20" s="8" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="C20" s="8" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="D20" s="2" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E20" s="2" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="F20" s="2" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G20" s="2" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A21" s="6" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B21" s="8" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="C21" s="7" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D21" s="2" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="E21" s="2" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F21" s="2" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G21" s="2" t="s">
+        <x:v>57</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A22" s="6" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B22" s="8" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="C22" s="8" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D22" s="2" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="E22" s="2" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="F22" s="2" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="G22" s="2" t="s">
+        <x:v>68</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A23" s="6" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B23" s="8" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="C23" s="8" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="D23" s="2" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="E23" s="2" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F23" s="2" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G23" s="2" t="s">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A24" s="6" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B24" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C24" s="8" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D24" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E24" s="2" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F24" s="2" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="G24" s="2" t="s">
+        <x:v>54</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A25" s="6" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="B25" s="8" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="C25" s="8" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D25" s="2" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B19" s="8" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="C19" s="8" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D19" s="2" t="s">
+      <x:c r="E25" s="2" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="F25" s="2" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G25" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A26" s="6" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B26" s="9" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="C26" s="9" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D26" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E26" s="2" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F26" s="2" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="G26" s="2" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="E19" s="2" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="F19" s="2" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="G19" s="2" t="s">
-        <x:v>37</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A20" s="6"/>
-      <x:c r="B20" s="8"/>
-      <x:c r="C20" s="8"/>
-    </x:row>
-    <x:row r="21" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A21" s="6"/>
-      <x:c r="B21" s="8"/>
-      <x:c r="C21" s="8"/>
-    </x:row>
-    <x:row r="22" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A22" s="6"/>
-      <x:c r="B22" s="8"/>
-      <x:c r="C22" s="8"/>
-    </x:row>
-    <x:row r="23" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A23" s="6"/>
-      <x:c r="B23" s="8"/>
-      <x:c r="C23" s="8"/>
-    </x:row>
-    <x:row r="24" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A24" s="6"/>
-      <x:c r="B24" s="8"/>
-      <x:c r="C24" s="8"/>
-    </x:row>
-    <x:row r="25" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A25" s="6"/>
-      <x:c r="B25" s="8"/>
-      <x:c r="C25" s="8"/>
-    </x:row>
-    <x:row r="26" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A26" s="6"/>
-      <x:c r="B26" s="9"/>
-      <x:c r="C26" s="9"/>
-    </x:row>
-    <x:row r="27" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A27" s="6"/>
-      <x:c r="B27" s="9"/>
-      <x:c r="C27" s="9"/>
+    </x:row>
+    <x:row r="27" spans="1:7" ht="15.75" customHeight="1">
+      <x:c r="A27" s="6" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="B27" s="9" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C27" s="9" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="D27" s="2" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="E27" s="2" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="F27" s="2" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="G27" s="2" t="s">
+        <x:v>53</x:v>
+      </x:c>
     </x:row>
     <x:row r="28" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A28" s="6"/>

--- a/JsonConverter/ExcelFiles/Cocktail.xlsx
+++ b/JsonConverter/ExcelFiles/Cocktail.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="24465" windowHeight="11745"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="29160" windowHeight="11745"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="126">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="150">
   <x:si>
     <x:t>거품 많은 드링크</x:t>
   </x:si>
@@ -25,6 +25,12 @@
     <x:t>MakeRecipe</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
   </x:si>
   <x:si>
@@ -142,6 +148,48 @@
     <x:t>그리즐리 템플</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Cocktail_SparkleStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_MoonBlast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_PianoMan_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Mercryblast_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_SunshineCloud_1</x:t>
   </x:si>
   <x:si>
@@ -151,6 +199,9 @@
     <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>머큐리 블라스트는 아델하이드 1, 브론순 추출액 1, 델타 가루 3, 플래너자이드 3, 카모트린 2 전부넣고 온더록스하고 혼합할 것.</x:t>
   </x:si>
   <x:si>
@@ -166,6 +217,9 @@
     <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
   </x:si>
   <x:si>
@@ -274,6 +328,12 @@
     <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>그리즐리 템플은 아델하이드 3, 브론순 추출액 3, 델타 가루 3, 카모트린 1 전부 넣고 혼합할 것.</x:t>
   </x:si>
   <x:si>
@@ -392,6 +452,18 @@
   </x:si>
   <x:si>
     <x:t>Cocktail_Mercuryblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_ZenStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Beer_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1674,91 +1746,93 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>4</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>3</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>32</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>107</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>120</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>51</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F4" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G4" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H4" s="4"/>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H4" s="3" t="s">
+        <x:v>56</x:v>
+      </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
       <x:c r="K4" s="4"/>
@@ -1767,27 +1841,29 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>121</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F5" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G5" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H5" s="4"/>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H5" s="3" t="s">
+        <x:v>44</x:v>
+      </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
       <x:c r="K5" s="4"/>
@@ -1796,27 +1872,29 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>123</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>84</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>87</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F6" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G6" s="4" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H6" s="4"/>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H6" s="5" t="s">
+        <x:v>54</x:v>
+      </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
       <x:c r="L6" s="4"/>
@@ -1824,27 +1902,29 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>112</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>99</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F7" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H7" s="4"/>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H7" s="6" t="s">
+        <x:v>53</x:v>
+      </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
       <x:c r="K7" s="4"/>
@@ -1853,27 +1933,29 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>118</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>21</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>61</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="F8" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G8" s="4" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="H8" s="4"/>
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H8" s="6" t="s">
+        <x:v>45</x:v>
+      </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
       <x:c r="K8" s="4"/>
@@ -1882,27 +1964,29 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>50</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F9" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G9" s="4" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="H9" s="4"/>
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H9" s="1" t="s">
+        <x:v>47</x:v>
+      </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
       <x:c r="K9" s="4"/>
@@ -1911,27 +1995,29 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D10" s="4" t="s">
         <x:v>16</x:v>
       </x:c>
-      <x:c r="D10" s="4" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F10" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G10" s="4" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H10" s="4"/>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H10" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
       <x:c r="K10" s="4"/>
@@ -1940,27 +2026,29 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>29</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>65</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="F11" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G11" s="4" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H11" s="4"/>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H11" s="6" t="s">
+        <x:v>105</x:v>
+      </x:c>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
       <x:c r="K11" s="4"/>
@@ -1969,27 +2057,29 @@
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>116</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>77</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F12" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G12" s="4" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="H12" s="4"/>
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="s">
+        <x:v>49</x:v>
+      </x:c>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>
       <x:c r="K12" s="4"/>
@@ -1998,27 +2088,29 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>72</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>115</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F13" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G13" s="4" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="H13" s="4"/>
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="s">
+        <x:v>50</x:v>
+      </x:c>
       <x:c r="I13" s="4"/>
       <x:c r="J13" s="4"/>
       <x:c r="K13" s="4"/>
@@ -2027,27 +2119,29 @@
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>71</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="E14" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F14" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G14" s="4" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H14" s="4"/>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H14" s="6" t="s">
+        <x:v>148</x:v>
+      </x:c>
       <x:c r="I14" s="4"/>
       <x:c r="J14" s="4"/>
       <x:c r="K14" s="4"/>
@@ -2056,307 +2150,345 @@
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>110</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
-        <x:v>106</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F15" s="4" t="s">
-        <x:v>58</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G15" s="4" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="H15" s="4"/>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H15" s="6" t="s">
+        <x:v>52</x:v>
+      </x:c>
       <x:c r="I15" s="4"/>
       <x:c r="J15" s="4"/>
       <x:c r="K15" s="4"/>
       <x:c r="L15" s="4"/>
       <x:c r="M15" s="4"/>
     </x:row>
-    <x:row r="16" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>108</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="C16" s="7" t="s">
-        <x:v>96</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>92</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F16" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G16" s="2" t="s">
-        <x:v>66</x:v>
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="H16" s="6" t="s">
+        <x:v>149</x:v>
       </x:c>
     </x:row>
-    <x:row r="17" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>122</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B17" s="8" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="C17" s="8" t="s">
-        <x:v>78</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F17" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>57</x:v>
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H17" s="6" t="s">
+        <x:v>46</x:v>
       </x:c>
     </x:row>
-    <x:row r="18" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>114</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B18" s="8" t="s">
-        <x:v>20</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="C18" s="8" t="s">
-        <x:v>104</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F18" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H18" s="6" t="s">
+        <x:v>147</x:v>
       </x:c>
     </x:row>
-    <x:row r="19" spans="1:7" ht="15.75" customHeight="1">
+    <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>113</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B19" s="8" t="s">
-        <x:v>22</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C19" s="8" t="s">
-        <x:v>19</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="F19" s="2" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G19" s="2" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H19" s="6" t="s">
+        <x:v>146</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A20" s="6" t="s">
+        <x:v>144</x:v>
+      </x:c>
+      <x:c r="B20" s="8" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C20" s="8" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D20" s="2" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="E20" s="2" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="F20" s="2" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G20" s="2" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H20" s="6" t="s">
+        <x:v>48</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A21" s="6" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B21" s="8" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C21" s="7" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D21" s="2" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="E21" s="2" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F21" s="2" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G21" s="2" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="H21" s="6" t="s">
+        <x:v>4</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A22" s="6" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B22" s="8" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="C22" s="8" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D22" s="2" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="E22" s="2" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="F22" s="2" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G22" s="2" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="H22" s="6" t="s">
+        <x:v>3</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A23" s="6" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="B23" s="8" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="C23" s="8" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="D23" s="2" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="E23" s="2" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F23" s="2" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G23" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H23" s="6" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A24" s="6" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B24" s="8" t="s">
+        <x:v>9</x:v>
+      </x:c>
+      <x:c r="C24" s="8" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="D24" s="2" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="E24" s="2" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F24" s="2" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="G24" s="2" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H24" s="6" t="s">
+        <x:v>61</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A25" s="6" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="B25" s="8" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="C25" s="8" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D25" s="2" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="E25" s="2" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="F25" s="2" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G25" s="2" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H25" s="6" t="s">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A26" s="6" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="B26" s="9" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="C26" s="9" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="D26" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="E26" s="2" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F26" s="2" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="G26" s="2" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H26" s="6" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="G19" s="2" t="s">
-        <x:v>53</x:v>
-      </x:c>
     </x:row>
-    <x:row r="20" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A20" s="6" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="B20" s="8" t="s">
-        <x:v>23</x:v>
-      </x:c>
-      <x:c r="C20" s="8" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="D20" s="2" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="E20" s="2" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="F20" s="2" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G20" s="2" t="s">
-        <x:v>55</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A21" s="6" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="B21" s="8" t="s">
+    <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A27" s="6" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="B27" s="9" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="C21" s="7" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="D21" s="2" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="E21" s="2" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F21" s="2" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G21" s="2" t="s">
+      <x:c r="C27" s="9" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="D27" s="2" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E27" s="2" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="F27" s="2" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G27" s="2" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H27" s="6" t="s">
         <x:v>57</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A22" s="6" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="B22" s="8" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C22" s="8" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D22" s="2" t="s">
-        <x:v>93</x:v>
-      </x:c>
-      <x:c r="E22" s="2" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="F22" s="2" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="G22" s="2" t="s">
-        <x:v>68</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A23" s="6" t="s">
-        <x:v>117</x:v>
-      </x:c>
-      <x:c r="B23" s="8" t="s">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C23" s="8" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="D23" s="2" t="s">
-        <x:v>102</x:v>
-      </x:c>
-      <x:c r="E23" s="2" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F23" s="2" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G23" s="2" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A24" s="6" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="B24" s="8" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C24" s="8" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="D24" s="2" t="s">
-        <x:v>45</x:v>
-      </x:c>
-      <x:c r="E24" s="2" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F24" s="2" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G24" s="2" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A25" s="6" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="B25" s="8" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="C25" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="D25" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="E25" s="2" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="F25" s="2" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G25" s="2" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A26" s="6" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="B26" s="9" t="s">
-        <x:v>26</x:v>
-      </x:c>
-      <x:c r="C26" s="9" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D26" s="2" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="E26" s="2" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F26" s="2" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="G26" s="2" t="s">
-        <x:v>56</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:7" ht="15.75" customHeight="1">
-      <x:c r="A27" s="6" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="B27" s="9" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C27" s="9" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="D27" s="2" t="s">
-        <x:v>90</x:v>
-      </x:c>
-      <x:c r="E27" s="2" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="F27" s="2" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G27" s="2" t="s">
-        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:3" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Cocktail.xlsx
+++ b/JsonConverter/ExcelFiles/Cocktail.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="29160" windowHeight="11745"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="18480" windowHeight="15165"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -14,456 +14,465 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="150">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="153">
+  <x:si>
+    <x:t>그리즐리 템플은 아델하이드 3, 브론순 추출액 3, 델타 가루 3, 카모트린 1 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"맛이 오래된 초콜릿 우유 같고 냄새도 꼭 그래. 어ᄄᅠᆫ 사람은 맛이 카라멜 캍다고 하기도 하고..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트는 브론순 추출액 6, 델타 가루 1, 플래너자이드 4, 카모트린 2 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Fail_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문블라스트는 아델하이드 6, 델타가루 1, 플래너자이드 1, 카모트린 2 전부 넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>각성용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판촉용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화끈함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단순함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행복함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제조법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoMan_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_ZenStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술을 제작하면서 어ᄄᅠᆫ 온도계도 피해입지 않았음을 알려드리는 바입니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"매달마다 1주일씩 관찰할 수 있는 월면 강입자포와는 아무런 연관이 없습니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이걸 마시면 자네가 술이 깨던가 차가움에 머리가 깨지던가, 둘 중 하나일 거야."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Fail_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 맨은 아델하이드 2, 브론순 추출액 3, 델타 가루 5, 플래너자이드 5, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션샤인 클라우드는 아델하이드 2, 브론순 추출액 2, 카모트린 추가 가능 전부 넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술은 술집 피아니스트 연맹 또는 구성원들의 의견을 대변하지 않습니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"거울 앞에 서서 블리딩 제인을 세 번 불러봐, 그럼 바보처럼 보일꺼야."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술이 쓰였던 영화의 팬이 아니라면, 이 술을 참기는 힘들것입니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인은 브론순 추출액 1, 델타 가루 3, 플래너자이드 3 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크는 델타 가루 2, 플래너자이드 4, 카모트린 추가 가능, 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
+  </x:si>
   <x:si>
     <x:t>거품 많은 드링크</x:t>
   </x:si>
   <x:si>
+    <x:t>MakeRecipe</x:t>
+  </x:si>
+  <x:si>
     <x:t>FromType</x:t>
   </x:si>
   <x:si>
-    <x:t>MakeRecipe</x:t>
+    <x:t>크레바스 스파이크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션샤인 클라우드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머큐리 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoodType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TasteType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극적인 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머큐리 블라스트는 아델하이드 1, 브론순 추출액 1, 델타 가루 3, 플래너자이드 3, 카모트린 2 전부넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 맨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그리즐리 템플</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급스러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시큼한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달콤한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쓴 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유서 깊음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_MoonBlast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SparkleStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_PianoMan_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SunshineCloud_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 한잔이면 충분히 그 행성처럼 얼굴이 붉게 된다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크레바스 스파이크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션샤인 클라우드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머큐리 블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 맨은 아델하이드 2, 브론순 추출액 3, 델타 가루 5, 플래너자이드 5, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블리딩 제인은 브론순 추출액 1, 델타 가루 3, 플래너자이드 3 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문 블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블리딩 제인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 맨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그리즐리 템플</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SparkleStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FrothyWater_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_GutPunch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_MoonBlast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FluffyDream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Piledriver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Brandtini_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BlueFairy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_PianoMan_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Mercryblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SunshineCloud_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GrlzzlyTemple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머큐리 블라스트는 아델하이드 1, 브론순 추출액 1, 델타 가루 3, 플래너자이드 3, 카모트린 2 전부넣고 온더록스하고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Cocktail_BleedingJane_1</x:t>
   </x:si>
   <x:si>
-    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 한잔이면 충분히 그 행성처럼 얼굴이 붉게 된다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화끈함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행복함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>각성용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단순함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판촉용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제조법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달콤한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시큼한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쓴 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유서 깊음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급스러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부드러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MoodType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GutPunch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_ZenStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Suplex_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoMan_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술을 제작하면서 어ᄄᅠᆫ 온도계도 피해입지 않았음을 알려드리는 바입니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"매달마다 1주일씩 관찰할 수 있는 월면 강입자포와는 아무런 연관이 없습니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이걸 마시면 자네가 술이 깨던가 차가움에 머리가 깨지던가, 둘 중 하나일 거야."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술이 쓰였던 영화의 팬이 아니라면, 이 술을 참기는 힘들것입니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술은 술집 피아니스트 연맹 또는 구성원들의 의견을 대변하지 않습니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"거울 앞에 서서 블리딩 제인을 세 번 불러봐, 그럼 바보처럼 보일꺼야."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
+    <x:t>Cocktail_Marsblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BleedingJane_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_MoonBlast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SugarRush_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_Suplex_1</x:t>
   </x:si>
   <x:si>
-    <x:t>그리즐리 템플은 아델하이드 3, 브론순 추출액 3, 델타 가루 3, 카모트린 1 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"맛이 오래된 초콜릿 우유 같고 냄새도 꼭 그래. 어ᄄᅠᆫ 사람은 맛이 카라멜 캍다고 하기도 하고..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스블라스트는 브론순 추출액 6, 델타 가루 1, 플래너자이드 4, 카모트린 2 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션샤인 클라우드는 아델하이드 2, 브론순 추출액 2, 카모트린 추가 가능 전부 넣고 온더록스하고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문블라스트는 아델하이드 6, 델타가루 1, 플래너자이드 1, 카모트린 2 전부 넣고 온더록스하고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크레바스 스파이크는 델타 가루 2, 플래너자이드 4, 카모트린 추가 가능, 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극적인 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TasteType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Piledriver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Mercryblast_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocktail_Brandtini_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocktail_CobaltVelvet_1</x:t>
   </x:si>
   <x:si>
-    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FluffyDream_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocktail_CreviceSpike_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BleedingJane_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocktail_SparkleStar_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_FrothyWater_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BlueFairy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_MoonBlast_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocktail_Mercuryblast_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Cocktail_ZenStar_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Marsblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F@####</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -642,7 +651,7 @@
       <x:alignment horizontal="general" vertical="center"/>
     </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="14">
+  <x:cellXfs count="15">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
@@ -685,6 +694,9 @@
     <x:xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="general" vertical="bottom"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="left" vertical="bottom" wrapText="1"/>
+    </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle xfId="0" builtinId="0"/>
@@ -695,6 +707,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -777,6 +790,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -811,6 +825,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -855,6 +870,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -898,6 +914,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -982,6 +999,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1002,6 +1020,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1032,6 +1051,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1746,92 +1766,92 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>5</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>77</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>34</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
-        <x:v>2</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>127</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>1</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>87</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>13</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>140</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>30</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>69</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F4" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G4" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H4" s="3" t="s">
-        <x:v>56</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1841,28 +1861,28 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>141</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>37</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>63</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>118</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F5" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G5" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H5" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1872,28 +1892,28 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>143</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>102</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F6" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G6" s="4" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H6" s="5" t="s">
-        <x:v>54</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1902,28 +1922,28 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>132</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>32</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>119</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F7" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H7" s="6" t="s">
-        <x:v>53</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1936,25 +1956,25 @@
         <x:v>138</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>66</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="E8" s="4" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="F8" s="4" t="s">
         <x:v>14</x:v>
       </x:c>
-      <x:c r="E8" s="4" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="F8" s="4" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="G8" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>45</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1964,28 +1984,28 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>68</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F9" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G9" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
@@ -1995,28 +2015,28 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>129</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>26</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F10" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G10" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
@@ -2026,28 +2046,28 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>121</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>83</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F11" s="4" t="s">
-        <x:v>82</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G11" s="4" t="s">
-        <x:v>72</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H11" s="6" t="s">
-        <x:v>105</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
@@ -2060,25 +2080,25 @@
         <x:v>136</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>33</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>95</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>120</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F12" s="4" t="s">
-        <x:v>81</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G12" s="4" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H12" s="6" t="s">
-        <x:v>49</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>
@@ -2088,28 +2108,28 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>90</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>135</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>111</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F13" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G13" s="4" t="s">
-        <x:v>84</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H13" s="6" t="s">
-        <x:v>50</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I13" s="4"/>
       <x:c r="J13" s="4"/>
@@ -2119,28 +2139,28 @@
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>89</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>10</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>125</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E14" s="4" t="s">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F14" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G14" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H14" s="6" t="s">
-        <x:v>148</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="I14" s="4"/>
       <x:c r="J14" s="4"/>
@@ -2150,28 +2170,28 @@
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>130</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
-        <x:v>126</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F15" s="4" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G15" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H15" s="6" t="s">
-        <x:v>52</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I15" s="4"/>
       <x:c r="J15" s="4"/>
@@ -2181,288 +2201,288 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>11</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="C16" s="7" t="s">
-        <x:v>116</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F16" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G16" s="2" t="s">
-        <x:v>84</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H16" s="6" t="s">
-        <x:v>149</x:v>
+        <x:v>150</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B17" s="8" t="s">
-        <x:v>42</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C17" s="8" t="s">
-        <x:v>96</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>114</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F17" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H17" s="6" t="s">
-        <x:v>46</x:v>
+        <x:v>108</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>134</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B18" s="8" t="s">
-        <x:v>22</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C18" s="8" t="s">
-        <x:v>124</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
-        <x:v>117</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F18" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H18" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>128</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>133</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B19" s="8" t="s">
-        <x:v>24</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C19" s="8" t="s">
-        <x:v>21</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="F19" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G19" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H19" s="6" t="s">
-        <x:v>146</x:v>
+        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="6" t="s">
-        <x:v>144</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B20" s="8" t="s">
-        <x:v>25</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="C20" s="8" t="s">
-        <x:v>94</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
-        <x:v>115</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="E20" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="F20" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="H20" s="6" t="s">
-        <x:v>48</x:v>
+        <x:v>107</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="6" t="s">
-        <x:v>59</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="B21" s="8" t="s">
-        <x:v>43</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C21" s="7" t="s">
-        <x:v>98</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
-        <x:v>106</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E21" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F21" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G21" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="H21" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>122</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="6" t="s">
-        <x:v>58</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B22" s="8" t="s">
-        <x:v>8</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C22" s="8" t="s">
-        <x:v>109</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D22" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E22" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F22" s="2" t="s">
-        <x:v>81</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G22" s="2" t="s">
-        <x:v>86</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H22" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>129</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A23" s="6" t="s">
-        <x:v>137</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B23" s="8" t="s">
-        <x:v>7</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C23" s="8" t="s">
-        <x:v>97</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D23" s="2" t="s">
-        <x:v>122</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E23" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F23" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G23" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H23" s="6" t="s">
-        <x:v>104</x:v>
+        <x:v>123</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A24" s="6" t="s">
-        <x:v>145</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B24" s="8" t="s">
-        <x:v>9</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C24" s="8" t="s">
-        <x:v>93</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D24" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E24" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F24" s="2" t="s">
-        <x:v>85</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G24" s="2" t="s">
-        <x:v>72</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H24" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="6" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B25" s="8" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B25" s="8" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="C25" s="8" t="s">
-        <x:v>99</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D25" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E25" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F25" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="G25" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H25" s="6" t="s">
-        <x:v>55</x:v>
+        <x:v>117</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="6" t="s">
-        <x:v>139</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B26" s="9" t="s">
-        <x:v>28</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C26" s="9" t="s">
-        <x:v>100</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D26" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E26" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F26" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G26" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="H26" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>130</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
@@ -2470,31 +2490,38 @@
         <x:v>131</x:v>
       </x:c>
       <x:c r="B27" s="9" t="s">
-        <x:v>41</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C27" s="9" t="s">
-        <x:v>70</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="D27" s="2" t="s">
-        <x:v>110</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="E27" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="F27" s="2" t="s">
-        <x:v>82</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="G27" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="H27" s="6" t="s">
-        <x:v>57</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
-    <x:row r="28" spans="1:3" ht="15.75" customHeight="1">
-      <x:c r="A28" s="6"/>
-      <x:c r="B28" s="9"/>
+    <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
+      <x:c r="A28" s="14" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="B28" s="9" t="s">
+        <x:v>152</x:v>
+      </x:c>
       <x:c r="C28" s="9"/>
+      <x:c r="H28" s="2" t="s">
+        <x:v>5</x:v>
+      </x:c>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
       <x:c r="A29" s="6"/>

--- a/JsonConverter/ExcelFiles/Cocktail.xlsx
+++ b/JsonConverter/ExcelFiles/Cocktail.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="18480" windowHeight="15165"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="25440" windowHeight="11190"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -16,463 +16,463 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="153">
   <x:si>
+    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인은 브론순 추출액 1, 델타 가루 3, 플래너자이드 3 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_MoonBlast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_PianoMan_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SunshineCloud_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SparkleStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Marsblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술을 제작하면서 어ᄄᅠᆫ 온도계도 피해입지 않았음을 알려드리는 바입니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"매달마다 1주일씩 관찰할 수 있는 월면 강입자포와는 아무런 연관이 없습니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이걸 마시면 자네가 술이 깨던가 차가움에 머리가 깨지던가, 둘 중 하나일 거야."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Fail_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 맨은 아델하이드 2, 브론순 추출액 3, 델타 가루 5, 플래너자이드 5, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크는 델타 가루 2, 플래너자이드 4, 카모트린 추가 가능, 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거품 많은 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TasteType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MakeRecipe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극적인 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션샤인 클라우드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머큐리 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoodType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FromType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CreviceSpike_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Marsblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Fail_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BleedingJane_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Mercuryblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_ZenStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SparkleStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_MoonBlast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술이 쓰였던 영화의 팬이 아니라면, 이 술을 참기는 힘들것입니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술은 술집 피아니스트 연맹 또는 구성원들의 의견을 대변하지 않습니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"거울 앞에 서서 블리딩 제인을 세 번 불러봐, 그럼 바보처럼 보일꺼야."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머큐리 블라스트는 아델하이드 1, 브론순 추출액 1, 델타 가루 3, 플래너자이드 3, 카모트린 2 전부넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 한잔이면 충분히 그 행성처럼 얼굴이 붉게 된다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_ZenStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoMan_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 맨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그리즐리 템플</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유서 깊음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시큼한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달콤한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급스러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F@####</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쓴 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행복함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제조법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>각성용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화끈함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단순함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판촉용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
     <x:t>그리즐리 템플은 아델하이드 3, 브론순 추출액 3, 델타 가루 3, 카모트린 1 전부 넣고 혼합할 것.</x:t>
   </x:si>
   <x:si>
-    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
+    <x:t>마스블라스트는 브론순 추출액 6, 델타 가루 1, 플래너자이드 4, 카모트린 2 전부 넣고 혼합할 것.</x:t>
   </x:si>
   <x:si>
     <x:t>"맛이 오래된 초콜릿 우유 같고 냄새도 꼭 그래. 어ᄄᅠᆫ 사람은 맛이 카라멜 캍다고 하기도 하고..."</x:t>
   </x:si>
   <x:si>
-    <x:t>마스블라스트는 브론순 추출액 6, 델타 가루 1, 플래너자이드 4, 카모트린 2 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Fail_1</x:t>
+    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션샤인 클라우드는 아델하이드 2, 브론순 추출액 2, 카모트린 추가 가능 전부 넣고 온더록스하고 혼합할 것.</x:t>
   </x:si>
   <x:si>
     <x:t>문블라스트는 아델하이드 6, 델타가루 1, 플래너자이드 1, 카모트린 2 전부 넣고 온더록스하고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>각성용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판촉용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화끈함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단순함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행복함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제조법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoMan_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Suplex_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_ZenStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GutPunch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술을 제작하면서 어ᄄᅠᆫ 온도계도 피해입지 않았음을 알려드리는 바입니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"매달마다 1주일씩 관찰할 수 있는 월면 강입자포와는 아무런 연관이 없습니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이걸 마시면 자네가 술이 깨던가 차가움에 머리가 깨지던가, 둘 중 하나일 거야."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Fail_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 맨은 아델하이드 2, 브론순 추출액 3, 델타 가루 5, 플래너자이드 5, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션샤인 클라우드는 아델하이드 2, 브론순 추출액 2, 카모트린 추가 가능 전부 넣고 온더록스하고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술은 술집 피아니스트 연맹 또는 구성원들의 의견을 대변하지 않습니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"거울 앞에 서서 블리딩 제인을 세 번 불러봐, 그럼 바보처럼 보일꺼야."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술이 쓰였던 영화의 팬이 아니라면, 이 술을 참기는 힘들것입니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블리딩 제인은 브론순 추출액 1, 델타 가루 3, 플래너자이드 3 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크레바스 스파이크는 델타 가루 2, 플래너자이드 4, 카모트린 추가 가능, 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거품 많은 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MakeRecipe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FromType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크레바스 스파이크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션샤인 클라우드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머큐리 블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MoodType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TasteType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극적인 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머큐리 블라스트는 아델하이드 1, 브론순 추출액 1, 델타 가루 3, 플래너자이드 3, 카모트린 2 전부넣고 온더록스하고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블리딩 제인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문 블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 맨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그리즐리 템플</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급스러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부드러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시큼한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달콤한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쓴 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유서 깊음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_MoonBlast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FrothyWater_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_GutPunch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Piledriver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FluffyDream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SparkleStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Brandtini_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BlueFairy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_PianoMan_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SunshineCloud_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GrlzzlyTemple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 한잔이면 충분히 그 행성처럼 얼굴이 붉게 된다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Marsblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BleedingJane_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Piledriver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_MoonBlast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FluffyDream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FrothyWater_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BlueFairy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Suplex_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Brandtini_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CobaltVelvet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CreviceSpike_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SparkleStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Mercuryblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_ZenStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Marsblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F@####</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -707,7 +707,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -790,7 +789,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -825,7 +823,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -870,7 +867,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -914,7 +910,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -999,7 +994,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1020,7 +1014,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1051,7 +1044,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1755,7 +1747,7 @@
   <x:dimension ref="A1:M35"/>
   <x:sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1"/>
   <x:cols>
-    <x:col min="1" max="1" width="19.42578125" style="2" customWidth="1"/>
+    <x:col min="1" max="1" width="27.85546875" style="2" customWidth="1"/>
     <x:col min="2" max="2" width="19.5703125" style="2" customWidth="1"/>
     <x:col min="3" max="3" width="50.7109375" style="2" customWidth="1"/>
     <x:col min="4" max="4" width="89" style="2" customWidth="1"/>
@@ -1766,92 +1758,92 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>22</x:v>
+        <x:v>133</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>13</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>18</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>90</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>68</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
-        <x:v>61</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>70</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>62</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>69</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>66</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>142</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>86</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D4" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="E4" s="4" t="s">
         <x:v>126</x:v>
       </x:c>
-      <x:c r="D4" s="4" t="s">
-        <x:v>50</x:v>
-      </x:c>
-      <x:c r="E4" s="4" t="s">
-        <x:v>101</x:v>
-      </x:c>
       <x:c r="F4" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G4" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H4" s="3" t="s">
-        <x:v>121</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1861,28 +1853,28 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>147</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>82</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>72</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F5" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G5" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H5" s="3" t="s">
-        <x:v>113</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1892,28 +1884,28 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>140</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>80</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>46</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F6" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G6" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H6" s="5" t="s">
-        <x:v>116</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1922,28 +1914,28 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>144</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>76</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>52</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>51</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F7" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H7" s="6" t="s">
-        <x:v>114</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1953,28 +1945,28 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>138</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>81</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>36</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F8" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G8" s="4" t="s">
-        <x:v>21</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>106</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1984,28 +1976,28 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>58</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F9" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G9" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
@@ -2015,28 +2007,28 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>133</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>47</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F10" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G10" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
@@ -2046,28 +2038,28 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>94</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>57</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>104</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F11" s="4" t="s">
-        <x:v>98</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G11" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H11" s="6" t="s">
-        <x:v>143</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
@@ -2077,28 +2069,28 @@
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>136</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>88</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>56</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F12" s="4" t="s">
-        <x:v>103</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G12" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H12" s="6" t="s">
-        <x:v>112</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>
@@ -2108,28 +2100,28 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>141</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F13" s="4" t="s">
-        <x:v>96</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G13" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H13" s="6" t="s">
-        <x:v>109</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I13" s="4"/>
       <x:c r="J13" s="4"/>
@@ -2139,28 +2131,28 @@
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>26</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>16</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="E14" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F14" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G14" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H14" s="6" t="s">
-        <x:v>149</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="I14" s="4"/>
       <x:c r="J14" s="4"/>
@@ -2170,28 +2162,28 @@
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>135</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F15" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G15" s="4" t="s">
-        <x:v>17</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H15" s="6" t="s">
-        <x:v>115</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="I15" s="4"/>
       <x:c r="J15" s="4"/>
@@ -2201,326 +2193,326 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>11</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>20</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="C16" s="7" t="s">
-        <x:v>7</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>37</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F16" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G16" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H16" s="6" t="s">
-        <x:v>150</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>139</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B17" s="8" t="s">
-        <x:v>102</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C17" s="8" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>38</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F17" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H17" s="6" t="s">
-        <x:v>108</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>145</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="B18" s="8" t="s">
-        <x:v>85</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C18" s="8" t="s">
-        <x:v>8</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
-        <x:v>59</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F18" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H18" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>137</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B19" s="8" t="s">
-        <x:v>79</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C19" s="8" t="s">
-        <x:v>75</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>60</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="F19" s="2" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="G19" s="2" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="H19" s="6" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="G19" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="H19" s="6" t="s">
-        <x:v>125</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="6" t="s">
-        <x:v>134</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="B20" s="8" t="s">
-        <x:v>87</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C20" s="8" t="s">
-        <x:v>29</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="E20" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F20" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="H20" s="6" t="s">
-        <x:v>107</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="6" t="s">
-        <x:v>119</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="B21" s="8" t="s">
-        <x:v>95</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C21" s="7" t="s">
-        <x:v>45</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
-        <x:v>0</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="E21" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F21" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G21" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="H21" s="6" t="s">
-        <x:v>122</x:v>
+        <x:v>91</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="6" t="s">
-        <x:v>118</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B22" s="8" t="s">
-        <x:v>65</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C22" s="8" t="s">
-        <x:v>3</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="D22" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E22" s="2" t="s">
-        <x:v>104</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F22" s="2" t="s">
-        <x:v>103</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="G22" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="H22" s="6" t="s">
-        <x:v>129</x:v>
+        <x:v>98</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A23" s="6" t="s">
-        <x:v>146</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B23" s="8" t="s">
-        <x:v>63</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C23" s="8" t="s">
-        <x:v>32</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="D23" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E23" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F23" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G23" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H23" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A24" s="6" t="s">
-        <x:v>148</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="B24" s="8" t="s">
-        <x:v>67</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C24" s="8" t="s">
-        <x:v>28</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D24" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E24" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F24" s="2" t="s">
-        <x:v>96</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G24" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="H24" s="6" t="s">
-        <x:v>124</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B25" s="8" t="s">
-        <x:v>92</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C25" s="8" t="s">
-        <x:v>41</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D25" s="2" t="s">
-        <x:v>35</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E25" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="F25" s="2" t="s">
-        <x:v>14</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="G25" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H25" s="6" t="s">
-        <x:v>117</x:v>
+        <x:v>20</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="6" t="s">
-        <x:v>132</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B26" s="9" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C26" s="9" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="C26" s="9" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="D26" s="2" t="s">
-        <x:v>48</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="E26" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F26" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="G26" s="2" t="s">
-        <x:v>12</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="H26" s="6" t="s">
-        <x:v>130</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A27" s="6" t="s">
-        <x:v>131</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B27" s="9" t="s">
-        <x:v>99</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="C27" s="9" t="s">
-        <x:v>127</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="D27" s="2" t="s">
-        <x:v>4</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="E27" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F27" s="2" t="s">
-        <x:v>98</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="G27" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="H27" s="6" t="s">
-        <x:v>151</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A28" s="14" t="s">
-        <x:v>33</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B28" s="9" t="s">
-        <x:v>152</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C28" s="9"/>
       <x:c r="H28" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Cocktail.xlsx
+++ b/JsonConverter/ExcelFiles/Cocktail.xlsx
@@ -4,7 +4,7 @@
   <x:fileVersion appName="HCell" lastEdited="10.0" lowestEdited="10.0" rupBuild="0.4575"/>
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <x:bookViews>
-    <x:workbookView xWindow="0" yWindow="0" windowWidth="25440" windowHeight="11190"/>
+    <x:workbookView xWindow="0" yWindow="0" windowWidth="22575" windowHeight="13110"/>
   </x:bookViews>
   <x:sheets>
     <x:sheet name="DNTable_Character&lt;Hero&gt;" sheetId="1" r:id="rId4"/>
@@ -16,463 +16,463 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="153">
   <x:si>
+    <x:t>"매달마다 1주일씩 관찰할 수 있는 월면 강입자포와는 아무런 연관이 없습니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이걸 마시면 자네가 술이 깨던가 차가움에 머리가 깨지던가, 둘 중 하나일 거야."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술을 제작하면서 어ᄄᅠᆫ 온도계도 피해입지 않았음을 알려드리는 바입니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머큐리 블라스트는 아델하이드 1, 브론순 추출액 1, 델타 가루 3, 플래너자이드 3, 카모트린 2 전부넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_ZenStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoMan_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인은 브론순 추출액 1, 델타 가루 3, 플래너자이드 3 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 맨은 아델하이드 2, 브론순 추출액 3, 델타 가루 5, 플래너자이드 5, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"거울 앞에 서서 블리딩 제인을 세 번 불러봐, 그럼 바보처럼 보일꺼야."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술이 쓰였던 영화의 팬이 아니라면, 이 술을 참기는 힘들것입니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술은 술집 피아니스트 연맹 또는 구성원들의 의견을 대변하지 않습니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그리즐리 템플</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 맨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션샤인 클라우드는 아델하이드 2, 브론순 추출액 2, 카모트린 추가 가능 전부 넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문블라스트는 아델하이드 6, 델타가루 1, 플래너자이드 1, 카모트린 2 전부 넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트는 브론순 추출액 6, 델타 가루 1, 플래너자이드 4, 카모트린 2 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"맛이 오래된 초콜릿 우유 같고 냄새도 꼭 그래. 어ᄄᅠᆫ 사람은 맛이 카라멜 캍다고 하기도 하고..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그리즐리 템플은 아델하이드 3, 브론순 추출액 3, 델타 가루 3, 카모트린 1 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TasteType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MakeRecipe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거품 많은 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극적인 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 한잔이면 충분히 그 행성처럼 얼굴이 붉게 된다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머큐리 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션샤인 클라우드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판촉용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화끈함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행복함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제조법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단순함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>각성용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoodType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FromType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
+  </x:si>
+  <x:si>
     <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
   </x:si>
   <x:si>
-    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
-  </x:si>
-  <x:si>
     <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
   </x:si>
   <x:si>
-    <x:t>Id</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블리딩 제인은 브론순 추출액 1, 델타 가루 3, 플래너자이드 3 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
+    <x:t>Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Fail_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달콤한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쓴 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급스러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유서 깊음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F@####</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시큼한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크는 델타 가루 2, 플래너자이드 4, 카모트린 추가 가능, 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_MoonBlast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BadTouch_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_PianoWoman_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_MoonBlast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Cocktail_GutPunch_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_FrothyWater_1</x:t>
+    <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_PianoMan_1</x:t>
   </x:si>
   <x:si>
-    <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Cocktail_Brandtini_1</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_SunshineCloud_1</x:t>
   </x:si>
   <x:si>
+    <x:t>Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Marsblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Cocktail_SugarRush_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_FluffyDream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GrlzzlyTemple_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Cocktail_Piledriver_1</x:t>
   </x:si>
   <x:si>
     <x:t>Icon/Cocktail_SparkleStar_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_BlueFairy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Marsblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술을 제작하면서 어ᄄᅠᆫ 온도계도 피해입지 않았음을 알려드리는 바입니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"매달마다 1주일씩 관찰할 수 있는 월면 강입자포와는 아무런 연관이 없습니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이걸 마시면 자네가 술이 깨던가 차가움에 머리가 깨지던가, 둘 중 하나일 거야."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Fail_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 맨은 아델하이드 2, 브론순 추출액 3, 델타 가루 5, 플래너자이드 5, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크레바스 스파이크는 델타 가루 2, 플래너자이드 4, 카모트린 추가 가능, 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거품 많은 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TasteType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MakeRecipe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극적인 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션샤인 클라우드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머큐리 블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크레바스 스파이크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MoodType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FromType</x:t>
+    <x:t>Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Fail_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BleedingJane_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Marsblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_MoonBlast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Mercuryblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_ZenStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Beer_1</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_CreviceSpike_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FluffyDream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Suplex_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Marsblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Fail_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BleedingJane_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocktail_FringeWeaver_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Mercuryblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_ZenStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Brandtini_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CobaltVelvet_1</x:t>
+    <x:t>Cocktail_Piledriver_1</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_SparkleStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FrothyWater_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BlueFairy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_MoonBlast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Piledriver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술이 쓰였던 영화의 팬이 아니라면, 이 술을 참기는 힘들것입니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술은 술집 피아니스트 연맹 또는 구성원들의 의견을 대변하지 않습니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"거울 앞에 서서 블리딩 제인을 세 번 불러봐, 그럼 바보처럼 보일꺼야."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머큐리 블라스트는 아델하이드 1, 브론순 추출액 1, 델타 가루 3, 플래너자이드 3, 카모트린 2 전부넣고 온더록스하고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 한잔이면 충분히 그 행성처럼 얼굴이 붉게 된다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_ZenStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoMan_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GutPunch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Suplex_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 맨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문 블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그리즐리 템플</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블리딩 제인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유서 깊음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시큼한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달콤한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급스러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부드러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F@####</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쓴 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행복함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제조법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>각성용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화끈함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단순함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판촉용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그리즐리 템플은 아델하이드 3, 브론순 추출액 3, 델타 가루 3, 카모트린 1 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스블라스트는 브론순 추출액 6, 델타 가루 1, 플래너자이드 4, 카모트린 2 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"맛이 오래된 초콜릿 우유 같고 냄새도 꼭 그래. 어ᄄᅠᆫ 사람은 맛이 카라멜 캍다고 하기도 하고..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션샤인 클라우드는 아델하이드 2, 브론순 추출액 2, 카모트린 추가 가능 전부 넣고 온더록스하고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문블라스트는 아델하이드 6, 델타가루 1, 플래너자이드 1, 카모트린 2 전부 넣고 온더록스하고 혼합할 것.</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -707,6 +707,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -789,6 +790,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -823,6 +825,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -867,6 +870,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -910,6 +914,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -994,6 +999,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1014,6 +1020,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1044,6 +1051,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1758,92 +1766,92 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>2</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>133</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>13</x:v>
+        <x:v>67</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>3</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>10</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E3" s="13" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="F3" s="13" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G3" s="13" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="H3" s="13" t="s">
         <x:v>53</x:v>
-      </x:c>
-      <x:c r="E3" s="13" t="s">
-        <x:v>52</x:v>
-      </x:c>
-      <x:c r="F3" s="13" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G3" s="13" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="H3" s="13" t="s">
-        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>78</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>116</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>92</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>126</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F4" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G4" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H4" s="3" t="s">
-        <x:v>24</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1853,28 +1861,28 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>74</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>120</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>87</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>126</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F5" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G5" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H5" s="3" t="s">
-        <x:v>28</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1884,28 +1892,28 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>76</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>109</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>86</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>142</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>126</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F6" s="4" t="s">
-        <x:v>128</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G6" s="4" t="s">
-        <x:v>129</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H6" s="5" t="s">
-        <x:v>29</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1914,28 +1922,28 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>72</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>118</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>48</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>126</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F7" s="4" t="s">
-        <x:v>127</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H7" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1945,28 +1953,28 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>68</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>107</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>39</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>126</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F8" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G8" s="4" t="s">
-        <x:v>132</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>15</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1976,28 +1984,28 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>43</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>143</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>131</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F9" s="4" t="s">
-        <x:v>121</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G9" s="4" t="s">
-        <x:v>141</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>18</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
@@ -2007,28 +2015,28 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>6</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>131</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F10" s="4" t="s">
-        <x:v>121</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G10" s="4" t="s">
-        <x:v>135</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>27</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
@@ -2038,28 +2046,28 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>103</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>119</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>44</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>131</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F11" s="4" t="s">
-        <x:v>121</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G11" s="4" t="s">
-        <x:v>135</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H11" s="6" t="s">
-        <x:v>63</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
@@ -2069,28 +2077,28 @@
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>62</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>112</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>32</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>45</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F12" s="4" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G12" s="4" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H12" s="6" t="s">
         <x:v>125</x:v>
-      </x:c>
-      <x:c r="F12" s="4" t="s">
-        <x:v>128</x:v>
-      </x:c>
-      <x:c r="G12" s="4" t="s">
-        <x:v>129</x:v>
-      </x:c>
-      <x:c r="H12" s="6" t="s">
-        <x:v>25</x:v>
       </x:c>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>
@@ -2100,28 +2108,28 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>101</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C13" s="3" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D13" s="4" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="E13" s="4" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="F13" s="4" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G13" s="4" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H13" s="6" t="s">
         <x:v>117</x:v>
-      </x:c>
-      <x:c r="C13" s="3" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="D13" s="4" t="s">
-        <x:v>150</x:v>
-      </x:c>
-      <x:c r="E13" s="4" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="F13" s="4" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="G13" s="4" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H13" s="6" t="s">
-        <x:v>17</x:v>
       </x:c>
       <x:c r="I13" s="4"/>
       <x:c r="J13" s="4"/>
@@ -2131,28 +2139,28 @@
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>99</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>137</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="D14" s="4" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D14" s="4" t="s">
-        <x:v>0</x:v>
-      </x:c>
       <x:c r="E14" s="4" t="s">
-        <x:v>125</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F14" s="4" t="s">
-        <x:v>139</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G14" s="4" t="s">
-        <x:v>136</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H14" s="6" t="s">
-        <x:v>71</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="I14" s="4"/>
       <x:c r="J14" s="4"/>
@@ -2162,28 +2170,28 @@
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="E15" s="4" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F15" s="4" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G15" s="4" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>115</x:v>
-      </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D15" s="4" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="E15" s="4" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="F15" s="4" t="s">
-        <x:v>139</x:v>
-      </x:c>
-      <x:c r="G15" s="4" t="s">
-        <x:v>136</x:v>
-      </x:c>
       <x:c r="H15" s="6" t="s">
-        <x:v>30</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="I15" s="4"/>
       <x:c r="J15" s="4"/>
@@ -2193,326 +2201,326 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>37</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>140</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C16" s="7" t="s">
-        <x:v>147</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="E16" s="2" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="F16" s="2" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G16" s="2" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H16" s="6" t="s">
         <x:v>148</x:v>
-      </x:c>
-      <x:c r="E16" s="2" t="s">
-        <x:v>51</x:v>
-      </x:c>
-      <x:c r="F16" s="2" t="s">
-        <x:v>138</x:v>
-      </x:c>
-      <x:c r="G16" s="2" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="H16" s="6" t="s">
-        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>75</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B17" s="8" t="s">
-        <x:v>122</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C17" s="8" t="s">
-        <x:v>33</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>149</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F17" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>136</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H17" s="6" t="s">
-        <x:v>19</x:v>
+        <x:v>115</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>73</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="B18" s="8" t="s">
-        <x:v>106</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C18" s="8" t="s">
-        <x:v>1</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
-        <x:v>47</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F18" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H18" s="6" t="s">
-        <x:v>93</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>67</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B19" s="8" t="s">
-        <x:v>108</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C19" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
-        <x:v>83</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="F19" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G19" s="2" t="s">
-        <x:v>141</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H19" s="6" t="s">
-        <x:v>96</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="6" t="s">
-        <x:v>77</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B20" s="8" t="s">
-        <x:v>110</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C20" s="8" t="s">
-        <x:v>35</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
-        <x:v>152</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E20" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="F20" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>132</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H20" s="6" t="s">
-        <x:v>16</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="6" t="s">
-        <x:v>26</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B21" s="8" t="s">
-        <x:v>111</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C21" s="7" t="s">
-        <x:v>81</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
-        <x:v>144</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E21" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F21" s="2" t="s">
-        <x:v>139</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G21" s="2" t="s">
-        <x:v>136</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="H21" s="6" t="s">
-        <x:v>91</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="6" t="s">
-        <x:v>23</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="B22" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C22" s="8" t="s">
-        <x:v>146</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D22" s="2" t="s">
-        <x:v>151</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="E22" s="2" t="s">
-        <x:v>131</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="F22" s="2" t="s">
-        <x:v>128</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G22" s="2" t="s">
-        <x:v>129</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H22" s="6" t="s">
-        <x:v>98</x:v>
+        <x:v>65</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A23" s="6" t="s">
-        <x:v>60</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B23" s="8" t="s">
-        <x:v>57</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C23" s="8" t="s">
-        <x:v>36</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D23" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="E23" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F23" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G23" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H23" s="6" t="s">
-        <x:v>94</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A24" s="6" t="s">
-        <x:v>69</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B24" s="8" t="s">
-        <x:v>56</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C24" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="D24" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E24" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F24" s="2" t="s">
-        <x:v>127</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G24" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="H24" s="6" t="s">
-        <x:v>90</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="6" t="s">
-        <x:v>100</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B25" s="8" t="s">
-        <x:v>104</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="C25" s="8" t="s">
-        <x:v>82</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D25" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E25" s="2" t="s">
-        <x:v>125</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="F25" s="2" t="s">
-        <x:v>139</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="G25" s="2" t="s">
-        <x:v>141</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H25" s="6" t="s">
-        <x:v>20</x:v>
+        <x:v>121</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="6" t="s">
-        <x:v>66</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B26" s="9" t="s">
-        <x:v>114</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C26" s="9" t="s">
-        <x:v>84</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="D26" s="2" t="s">
-        <x:v>8</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E26" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F26" s="2" t="s">
-        <x:v>138</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G26" s="2" t="s">
-        <x:v>134</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="H26" s="6" t="s">
-        <x:v>95</x:v>
+        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A27" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="B27" s="9" t="s">
-        <x:v>124</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C27" s="9" t="s">
-        <x:v>97</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="D27" s="2" t="s">
-        <x:v>145</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E27" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F27" s="2" t="s">
-        <x:v>121</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G27" s="2" t="s">
-        <x:v>141</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H27" s="6" t="s">
-        <x:v>31</x:v>
+        <x:v>126</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A28" s="14" t="s">
-        <x:v>38</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B28" s="9" t="s">
-        <x:v>130</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C28" s="9"/>
       <x:c r="H28" s="2" t="s">
-        <x:v>65</x:v>
+        <x:v>135</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Cocktail.xlsx
+++ b/JsonConverter/ExcelFiles/Cocktail.xlsx
@@ -16,19 +16,184 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="153">
   <x:si>
+    <x:t>Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoMan_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_ZenStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Fail_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션샤인 클라우드는 아델하이드 2, 브론순 추출액 2, 카모트린 추가 가능 전부 넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트는 브론순 추출액 6, 델타 가루 1, 플래너자이드 4, 카모트린 2 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"맛이 오래된 초콜릿 우유 같고 냄새도 꼭 그래. 어ᄄᅠᆫ 사람은 맛이 카라멜 캍다고 하기도 하고..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그리즐리 템플은 아델하이드 3, 브론순 추출액 3, 델타 가루 3, 카모트린 1 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 한잔이면 충분히 그 행성처럼 얼굴이 붉게 된다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인은 브론순 추출액 1, 델타 가루 3, 플래너자이드 3 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크는 델타 가루 2, 플래너자이드 4, 카모트린 추가 가능, 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 맨은 아델하이드 2, 브론순 추출액 3, 델타 가루 5, 플래너자이드 5, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"거울 앞에 서서 블리딩 제인을 세 번 불러봐, 그럼 바보처럼 보일꺼야."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술이 쓰였던 영화의 팬이 아니라면, 이 술을 참기는 힘들것입니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술은 술집 피아니스트 연맹 또는 구성원들의 의견을 대변하지 않습니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문블라스트는 아델하이드 6, 델타 가루 1, 플래너자이드 1, 카모트린 2 전부 넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이걸 마시면 자네가 술이 깨던가 차가움에 머리가 깨지던가, 둘 중 하나일 거야."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술을 제작하면서 어ᄄᅠᆫ 온도계도 피해입지 않았음을 알려드리는 바입니다."</x:t>
+  </x:si>
+  <x:si>
     <x:t>"매달마다 1주일씩 관찰할 수 있는 월면 강입자포와는 아무런 연관이 없습니다."</x:t>
   </x:si>
   <x:si>
-    <x:t>"이걸 마시면 자네가 술이 깨던가 차가움에 머리가 깨지던가, 둘 중 하나일 거야."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술을 제작하면서 어ᄄᅠᆫ 온도계도 피해입지 않았음을 알려드리는 바입니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
+    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
   </x:si>
   <x:si>
     <x:t>머큐리 블라스트는 아델하이드 1, 브론순 추출액 1, 델타 가루 3, 플래너자이드 3, 카모트린 2 전부넣고 온더록스하고 혼합할 것.</x:t>
@@ -37,136 +202,181 @@
     <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
   </x:si>
   <x:si>
-    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Suplex_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_ZenStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GutPunch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoMan_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블리딩 제인은 브론순 추출액 1, 델타 가루 3, 플래너자이드 3 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
+    <x:t>강함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화끈함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행복함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판촉용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단순함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제조법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>각성용</x:t>
   </x:si>
   <x:si>
     <x:t>Id</x:t>
   </x:si>
   <x:si>
-    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 맨은 아델하이드 2, 브론순 추출액 3, 델타 가루 5, 플래너자이드 5, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"거울 앞에 서서 블리딩 제인을 세 번 불러봐, 그럼 바보처럼 보일꺼야."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술이 쓰였던 영화의 팬이 아니라면, 이 술을 참기는 힘들것입니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술은 술집 피아니스트 연맹 또는 구성원들의 의견을 대변하지 않습니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
+    <x:t>블루 페어리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>여성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>남성적임</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>string</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그리즐리 템플</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
   </x:si>
   <x:si>
     <x:t>피아노 우먼</x:t>
   </x:si>
   <x:si>
-    <x:t>파일 드라이버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그리즐리 템플</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳</x:t>
-  </x:si>
-  <x:si>
     <x:t>피아노 맨</x:t>
   </x:si>
   <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문 블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션샤인 클라우드는 아델하이드 2, 브론순 추출액 2, 카모트린 추가 가능 전부 넣고 온더록스하고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문블라스트는 아델하이드 6, 델타가루 1, 플래너자이드 1, 카모트린 2 전부 넣고 온더록스하고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스블라스트는 브론순 추출액 6, 델타 가루 1, 플래너자이드 4, 카모트린 2 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"맛이 오래된 초콜릿 우유 같고 냄새도 꼭 그래. 어ᄄᅠᆫ 사람은 맛이 카라멜 캍다고 하기도 하고..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그리즐리 템플은 아델하이드 3, 브론순 추출액 3, 델타 가루 3, 카모트린 1 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달콤한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유서 깊음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>부드러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쓴 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시큼한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급스러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>F@####</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_MoonBlast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SunshineCloud_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GutPunch_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_PianoMan_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SparkleStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Marsblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
   </x:si>
   <x:si>
     <x:t>TasteType</x:t>
@@ -175,298 +385,88 @@
     <x:t>MakeRecipe</x:t>
   </x:si>
   <x:si>
+    <x:t>자극적인 드링크</x:t>
+  </x:si>
+  <x:si>
     <x:t>IconPath</x:t>
   </x:si>
   <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
     <x:t>거품 많은 드링크</x:t>
   </x:si>
   <x:si>
-    <x:t>자극적인 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 한잔이면 충분히 그 행성처럼 얼굴이 붉게 된다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>string</x:t>
+    <x:t>FromType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoodType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션샤인 클라우드</x:t>
   </x:si>
   <x:si>
     <x:t>머큐리 블라스트</x:t>
   </x:si>
   <x:si>
-    <x:t>션샤인 클라우드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판촉용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화끈함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행복함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제조법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단순함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>각성용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MoodType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FromType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크레바스 스파이크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Fail_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>여성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>남성적임</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블리딩 제인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달콤한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쓴 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급스러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유서 깊음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부드러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F@####</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시큼한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크레바스 스파이크는 델타 가루 2, 플래너자이드 4, 카모트린 추가 가능, 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FrothyWater_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_MoonBlast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_GutPunch_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_PianoMan_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Brandtini_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SunshineCloud_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GrlzzlyTemple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FluffyDream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Marsblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BlueFairy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Piledriver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SparkleStar_1</x:t>
+    <x:t>Cocktail_MoonBlast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BleedingJane_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Mercuryblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_ZenStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Fail_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CreviceSpike_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FringeWeaver_1</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_Brandtini_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_Suplex_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Fail_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FrothyWater_1</x:t>
+    <x:t>Cocktail_FluffyDream_1</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_BlueFairy_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_FluffyDream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BleedingJane_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocktail_Marsblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_MoonBlast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CobaltVelvet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Mercuryblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_ZenStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CreviceSpike_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FringeWeaver_1</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_Piledriver_1</x:t>
@@ -707,7 +707,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -790,7 +789,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -825,7 +823,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -870,7 +867,6 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -914,7 +910,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -999,7 +994,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1020,7 +1014,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1051,7 +1044,6 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
-            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1766,92 +1758,92 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>78</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>19</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>35</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>13</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
-        <x:v>52</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>51</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>82</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>81</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>53</x:v>
+        <x:v>124</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>143</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>104</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>57</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>15</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F4" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G4" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H4" s="3" t="s">
-        <x:v>129</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1864,25 +1856,25 @@
         <x:v>152</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>99</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>6</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>108</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F5" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G5" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H5" s="3" t="s">
-        <x:v>131</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1892,28 +1884,28 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>138</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>39</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>28</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>48</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F6" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G6" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H6" s="5" t="s">
-        <x:v>127</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1922,28 +1914,28 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>132</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>102</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>111</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F7" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H7" s="6" t="s">
-        <x:v>122</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1953,28 +1945,28 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>134</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>29</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>20</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F8" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G8" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>118</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1984,28 +1976,28 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>11</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>110</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>50</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F9" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G9" s="4" t="s">
-        <x:v>71</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
@@ -2018,25 +2010,25 @@
         <x:v>151</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>18</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F10" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G10" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>130</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
@@ -2046,28 +2038,28 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>8</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>96</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>107</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F11" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G11" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H11" s="6" t="s">
-        <x:v>133</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
@@ -2077,28 +2069,28 @@
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>139</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>36</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>109</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F12" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G12" s="4" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H12" s="6" t="s">
-        <x:v>125</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>
@@ -2108,28 +2100,28 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>9</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
         <x:v>136</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>43</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F13" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G13" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H13" s="6" t="s">
-        <x:v>117</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="I13" s="4"/>
       <x:c r="J13" s="4"/>
@@ -2139,28 +2131,28 @@
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>10</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>72</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
-        <x:v>85</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E14" s="4" t="s">
-        <x:v>105</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F14" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G14" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H14" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="I14" s="4"/>
       <x:c r="J14" s="4"/>
@@ -2170,28 +2162,28 @@
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>145</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>120</x:v>
       </x:c>
       <x:c r="D15" s="4" t="s">
-        <x:v>7</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E15" s="4" t="s">
-        <x:v>55</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F15" s="4" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G15" s="4" t="s">
-        <x:v>79</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H15" s="6" t="s">
-        <x:v>128</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="I15" s="4"/>
       <x:c r="J15" s="4"/>
@@ -2201,326 +2193,326 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
-        <x:v>87</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B16" s="7" t="s">
-        <x:v>77</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C16" s="7" t="s">
-        <x:v>40</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D16" s="2" t="s">
-        <x:v>41</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E16" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F16" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G16" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="H16" s="6" t="s">
-        <x:v>148</x:v>
+        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>137</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="B17" s="8" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="C17" s="8" t="s">
-        <x:v>4</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>42</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F17" s="2" t="s">
-        <x:v>76</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H17" s="6" t="s">
-        <x:v>115</x:v>
+        <x:v>104</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>144</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="B18" s="8" t="s">
-        <x:v>33</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C18" s="8" t="s">
-        <x:v>84</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
-        <x:v>112</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F18" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H18" s="6" t="s">
-        <x:v>58</x:v>
+        <x:v>21</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>150</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="B19" s="8" t="s">
-        <x:v>32</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C19" s="8" t="s">
-        <x:v>70</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
-        <x:v>27</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>54</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="F19" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G19" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H19" s="6" t="s">
-        <x:v>64</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="6" t="s">
-        <x:v>142</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B20" s="8" t="s">
-        <x:v>37</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C20" s="8" t="s">
-        <x:v>0</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E20" s="2" t="s">
-        <x:v>93</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F20" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H20" s="6" t="s">
-        <x:v>116</x:v>
+        <x:v>105</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="6" t="s">
-        <x:v>124</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="B21" s="8" t="s">
-        <x:v>31</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C21" s="7" t="s">
-        <x:v>25</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
-        <x:v>49</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="E21" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F21" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G21" s="2" t="s">
-        <x:v>79</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H21" s="6" t="s">
-        <x:v>59</x:v>
+        <x:v>29</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="6" t="s">
-        <x:v>123</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="B22" s="8" t="s">
-        <x:v>69</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C22" s="8" t="s">
-        <x:v>47</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D22" s="2" t="s">
-        <x:v>44</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E22" s="2" t="s">
-        <x:v>94</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="F22" s="2" t="s">
-        <x:v>89</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G22" s="2" t="s">
-        <x:v>101</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H22" s="6" t="s">
-        <x:v>65</x:v>
+        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A23" s="6" t="s">
-        <x:v>149</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="B23" s="8" t="s">
-        <x:v>83</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="C23" s="8" t="s">
-        <x:v>1</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D23" s="2" t="s">
-        <x:v>113</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="E23" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F23" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G23" s="2" t="s">
-        <x:v>80</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H23" s="6" t="s">
-        <x:v>61</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A24" s="6" t="s">
-        <x:v>146</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="B24" s="8" t="s">
-        <x:v>68</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C24" s="8" t="s">
-        <x:v>2</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D24" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E24" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F24" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="G24" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H24" s="6" t="s">
-        <x:v>60</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="6" t="s">
-        <x:v>12</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B25" s="8" t="s">
-        <x:v>34</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C25" s="8" t="s">
-        <x:v>26</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D25" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E25" s="2" t="s">
-        <x:v>105</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="F25" s="2" t="s">
-        <x:v>73</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G25" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H25" s="6" t="s">
-        <x:v>121</x:v>
+        <x:v>116</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="6" t="s">
-        <x:v>140</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="B26" s="9" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C26" s="9" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D26" s="2" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="E26" s="2" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="F26" s="2" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G26" s="2" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="H26" s="6" t="s">
         <x:v>24</x:v>
-      </x:c>
-      <x:c r="D26" s="2" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="E26" s="2" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="F26" s="2" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G26" s="2" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="H26" s="6" t="s">
-        <x:v>62</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A27" s="6" t="s">
-        <x:v>141</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="B27" s="9" t="s">
-        <x:v>95</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C27" s="9" t="s">
-        <x:v>63</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="D27" s="2" t="s">
-        <x:v>46</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E27" s="2" t="s">
-        <x:v>55</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="F27" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G27" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H27" s="6" t="s">
-        <x:v>126</x:v>
+        <x:v>119</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A28" s="14" t="s">
-        <x:v>88</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="B28" s="9" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="C28" s="9"/>
       <x:c r="H28" s="2" t="s">
-        <x:v>135</x:v>
+        <x:v>142</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">

--- a/JsonConverter/ExcelFiles/Cocktail.xlsx
+++ b/JsonConverter/ExcelFiles/Cocktail.xlsx
@@ -16,223 +16,322 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="153">
   <x:si>
+    <x:t>Cocktail_FrothyWater_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BleedingJane_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_MoonBlast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SugarRush_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Mercuryblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_ZenStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Suplex_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CreviceSpike_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Fail_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SparkleStar_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Marsblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Brandtini_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션샤인 클라우드는 아델하이드 2, 브론순 추출액 2, 카모트린 추가 가능 전부 넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Fail_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_Beer_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>각성용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화끈함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>행복함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>제조법</x:t>
+  </x:si>
+  <x:si>
+    <x:t>클래식</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단순함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>강함</x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주</x:t>
+  </x:si>
+  <x:si>
+    <x:t>젠스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Id</x:t>
+  </x:si>
+  <x:si>
+    <x:t>판촉용</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_PianoMan_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_BadTouch_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Cocktail_GutPunch_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Cocktail_PianoMan_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BadTouch_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Cocktail_ZenStar_1</x:t>
   </x:si>
   <x:si>
     <x:t>Cocktail_Suplex_1</x:t>
   </x:si>
   <x:si>
+    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머큐리 블라스트는 아델하이드 1, 브론순 추출액 1, 델타 가루 3, 플래너자이드 3, 카모트린 2 전부넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>문블라스트는 아델하이드 6, 델타 가루 1, 플래너자이드 1, 카모트린 2 전부 넣고 온더록스하고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이걸 마시면 자네가 술이 깨던가 차가움에 머리가 깨지던가, 둘 중 하나일 거야."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술을 제작하면서 어ᄄᅠᆫ 온도계도 피해입지 않았음을 알려드리는 바입니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"매달마다 1주일씩 관찰할 수 있는 월면 강입자포와는 아무런 연관이 없습니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인은 브론순 추출액 1, 델타 가루 3, 플래너자이드 3 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 한잔이면 충분히 그 행성처럼 얼굴이 붉게 된다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 따라준거 같네만..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크는 델타 가루 2, 플래너자이드 4, 카모트린 추가 가능, 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
+  </x:si>
+  <x:si>
+    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"거울 앞에 서서 블리딩 제인을 세 번 불러봐, 그럼 바보처럼 보일꺼야."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술은 술집 피아니스트 연맹 또는 구성원들의 의견을 대변하지 않습니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이 술이 쓰였던 영화의 팬이 아니라면, 이 술을 참기는 힘들것입니다."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트는 브론순 추출액 6, 델타 가루 1, 플래너자이드 4, 카모트린 2 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"맛이 오래된 초콜릿 우유 같고 냄새도 꼭 그래. 어ᄄᅠᆫ 사람은 맛이 카라멜 캍다고 하기도 하고..."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그리즐리 템플은 아델하이드 3, 브론순 추출액 3, 델타 가루 3, 카모트린 1 전부 넣고 혼합할 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 맨은 아델하이드 2, 브론순 추출액 3, 델타 가루 5, 플래너자이드 5, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Description</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MoodType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>크레바스 스파이크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TasteType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FromType</x:t>
+  </x:si>
+  <x:si>
+    <x:t>션샤인 클라우드</x:t>
+  </x:si>
+  <x:si>
+    <x:t>머큐리 블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>자극적인 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>거품 많은 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MakeRecipe</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IconPath</x:t>
+  </x:si>
+  <x:si>
+    <x:t>캐릭터 고유 ID</x:t>
+  </x:si>
+  <x:si>
     <x:t>"이거 꼭 에틸알코올에 설탕 한 숟같 타서 마시는 것 같네...."</x:t>
   </x:si>
   <x:si>
-    <x:t>"이거 꼭 콜라 남은 컵에 샴페인 ᄄᆞ라준거 같네만..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠 스타는 모든 재료를 4개씩 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Fail_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 전체 컨셉이나 스토리</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">"전통 방식으로 양조된 맥주는 고급품이 되었지만, 이정도면 원조와 거의 비슷하다고 할 수 있을것이다...." </x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주는 아델하이드 1, 브론순 추출액 2, 델타 가루 1, 플래너자이드 2, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프로씨 워터는 아델하이드 1, 브론순 추출액 1, 델타 가루 1, 플래너자이드 1 전부 넣고 숙성시키고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치는 브론순 추출액 2, 델타 가루 2, 플래너자이드 2, 카모트린 4 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션샤인 클라우드는 아델하이드 2, 브론순 추출액 2, 카모트린 추가 가능 전부 넣고 온더록스하고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블루 페어리는 아델하이드 4, 플래너자이드 1, 카모트린 추가 가능, 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스블라스트는 브론순 추출액 6, 델타 가루 1, 플래너자이드 4, 카모트린 2 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"맛이 오래된 초콜릿 우유 같고 냄새도 꼭 그래. 어ᄄᅠᆫ 사람은 맛이 카라멜 캍다고 하기도 하고..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>그리즐리 템플은 아델하이드 3, 브론순 추출액 3, 델타 가루 3, 카모트린 1 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거트 펀치는 브론순 추출액 5, 플래너자이드 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_CobaltVelvet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Mercuryblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"상큼하게, 맑게, 자신 있게, 이걸 마시는 여성처럼"</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BleedingJane_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_SunshineCloud_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이거 한잔이면 충분히 그 행성처럼 얼굴이 붉게 된다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_CreviceSpike_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_GrlzzlyTemple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Description</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이걸 마신다고 혀를 다치거나 하진 않아, 그래도 목 아플때는 마시지 않는게 좋을걸..."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>슈가 러쉬는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능, 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블리딩 제인은 브론순 추출액 1, 델타 가루 3, 플래너자이드 3 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>브랜티니는 아델하이드 6, 델타 가루 3, 카모트린 1 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>파일 드라이버는 브론순 추출액 3, 플래너자이드 3, 카모트린 4 전부 넣고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스는 브론순 추출액 4, 플래너자이드, 3, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타는 아델하이드 2, 델타 가루 1, 카모트린 추가 가능 전부 넣고 숙성시키고 섞을 것,</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림은 아델하이드 3, 델타 가루 3 카모트린 추가 가능. 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 '내장으로 만든 펀치'라는 뜻인데, 사실은 이걸 마시면 드는 느낌에 따라 붙인 이름이다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크레바스 스파이크는 델타 가루 2, 플래너자이드 4, 카모트린 추가 가능, 전부 넣고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"잘난 척하는 똥꼬놈들 십중팔구가 이걸 원하지만, 그놈들 똥꼬가 잘난 척하느라 너무 바쁘다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"파일 드라이버랑 살짝 다른데 혀가 불타는 맛이 좀 더 강조되고 목이 타는 느낌은 좀 줄었어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳은 아델하이드 2, 플래너자이드 3 ,카모트린 5, 전부 넣고 온더록스하고 섞을 것</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 원래 프리티 우먼이라고 불렸던 건데, 피아노 맨이 있으면 피아노 우먼도 있어야 하는 거 아니냐는 사람들이 있어서 그만."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 맨은 아델하이드 2, 브론순 추출액 3, 델타 가루 5, 플래너자이드 5, 카모트린 3 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼은 아델하이드 5, 브론순 추출액 5, 델타 가루 2, 플래너자이드 3, 카모트린 3 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"재료 비율이 균형 잡혀 있다면 더 맛있을 것 같은가요? 절대 아닙니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"한 잔만 마셔도 이가 전부 파란색으로 변한다, 양치질 잘하길 바란다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"거울 앞에 서서 블리딩 제인을 세 번 불러봐, 그럼 바보처럼 보일꺼야."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술이 쓰였던 영화의 팬이 아니라면, 이 술을 참기는 힘들것입니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술은 술집 피아니스트 연맹 또는 구성원들의 의견을 대변하지 않습니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>프린지 위버는 아델하이드 1, 카모트린 9 전부 넣고 숙성시키고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>문블라스트는 아델하이드 6, 델타 가루 1, 플래너자이드 1, 카모트린 2 전부 넣고 온더록스하고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"두어 잔 마시면 혀가 부-드럽게 풀리고, 좀 더 마시면 죽은 듯이 자게 될 거다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이걸 마시면 자네가 술이 깨던가 차가움에 머리가 깨지던가, 둘 중 하나일 거야."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"2040년 이래로 12세 이상 시청가 방송에서 계속 사랑받아온 맥주 대용품."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이 술을 제작하면서 어ᄄᅠᆫ 온도계도 피해입지 않았음을 알려드리는 바입니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"매달마다 1주일씩 관찰할 수 있는 월면 강입자포와는 아무런 연관이 없습니다."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트는 아델하이드 4, 델타 가루 1, 플래너자이드 2 와 카모트린 3 전부 숙성시키고, 전부 넣고 온더록스하고 섞을 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머큐리 블라스트는 아델하이드 1, 브론순 추출액 1, 델타 가루 3, 플래너자이드 3, 카모트린 2 전부넣고 온더록스하고 혼합할 것.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"이건 원래 실제로 쏘는 맛이 있었는데, 사람들이 이걸 마시면 피부 트러블이 생긴다는 불만이 폭주해서 탄산 없이 다시 만들어졌어."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>강함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화끈함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>행복함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>맥주</x:t>
-  </x:si>
-  <x:si>
-    <x:t>젠스타</x:t>
-  </x:si>
-  <x:si>
-    <x:t>판촉용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>클래식</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단순함</x:t>
-  </x:si>
-  <x:si>
-    <x:t>제조법</x:t>
-  </x:si>
-  <x:si>
-    <x:t>각성용</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Id</x:t>
+    <x:t>남성적임</x:t>
   </x:si>
   <x:si>
     <x:t>블루 페어리</x:t>
@@ -241,123 +340,120 @@
     <x:t>여성적임</x:t>
   </x:si>
   <x:si>
-    <x:t>남성적임</x:t>
-  </x:si>
-  <x:si>
     <x:t>프린지 위버</x:t>
   </x:si>
   <x:si>
+    <x:t>부드러움</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블리딩 제인</x:t>
+  </x:si>
+  <x:si>
+    <x:t>스파클 스타</x:t>
+  </x:si>
+  <x:si>
+    <x:t>그리즐리 템플</x:t>
+  </x:si>
+  <x:si>
+    <x:t>피아노 우먼</x:t>
+  </x:si>
+  <x:si>
     <x:t>string</x:t>
   </x:si>
   <x:si>
     <x:t>거트 펀치</x:t>
   </x:si>
   <x:si>
+    <x:t>Name</x:t>
+  </x:si>
+  <x:si>
+    <x:t>플러피 드림</x:t>
+  </x:si>
+  <x:si>
+    <x:t>(name)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>달콤한 드링크</x:t>
+  </x:si>
+  <x:si>
     <x:t>문 블라스트</x:t>
   </x:si>
   <x:si>
+    <x:t>피아노 맨</x:t>
+  </x:si>
+  <x:si>
+    <x:t>코발트 벨벳</x:t>
+  </x:si>
+  <x:si>
+    <x:t>유서 깊음</x:t>
+  </x:si>
+  <x:si>
+    <x:t>쓴 드링크</x:t>
+  </x:si>
+  <x:si>
     <x:t>파일 드라이버</x:t>
   </x:si>
   <x:si>
-    <x:t>그리즐리 템플</x:t>
-  </x:si>
-  <x:si>
-    <x:t>코발트 벨벳</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Name</x:t>
-  </x:si>
-  <x:si>
-    <x:t>플러피 드림</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 우먼</x:t>
-  </x:si>
-  <x:si>
-    <x:t>피아노 맨</x:t>
-  </x:si>
-  <x:si>
-    <x:t>(name)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>달콤한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>유서 깊음</x:t>
-  </x:si>
-  <x:si>
-    <x:t>부드러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>쓴 드링크</x:t>
-  </x:si>
-  <x:si>
     <x:t>프로씨 워터</x:t>
   </x:si>
   <x:si>
-    <x:t>블리딩 제인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>스파클 스타</x:t>
+    <x:t>F@####</x:t>
+  </x:si>
+  <x:si>
+    <x:t>슈가 러쉬</x:t>
+  </x:si>
+  <x:si>
+    <x:t>블룸 라이트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>마스블라스트</x:t>
+  </x:si>
+  <x:si>
+    <x:t>시큼한 드링크</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수플렉스</x:t>
+  </x:si>
+  <x:si>
+    <x:t>배드 터치</x:t>
+  </x:si>
+  <x:si>
+    <x:t>고급스러움</x:t>
   </x:si>
   <x:si>
     <x:t>브랜티니</x:t>
   </x:si>
   <x:si>
-    <x:t>슈가 러쉬</x:t>
-  </x:si>
-  <x:si>
-    <x:t>시큼한 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>마스블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>블룸 라이트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>고급스러움</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수플렉스</x:t>
-  </x:si>
-  <x:si>
-    <x:t>배드 터치</x:t>
-  </x:si>
-  <x:si>
-    <x:t>F@####</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Cocktail_FrothyWater_1</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Cocktail_PianoWoman_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_FluffyDream_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Cocktail_MoonBlast_1</x:t>
   </x:si>
   <x:si>
+    <x:t>Icon/Cocktail_Piledriver_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_GrlzzlyTemple_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cocktail_SunshineCloud_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BlueFairy_1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Icon/Cocktail_BloomLight_1</x:t>
+  </x:si>
+  <x:si>
     <x:t>Icon/Cocktail_BadTouch_1</x:t>
   </x:si>
   <x:si>
-    <x:t>Icon/Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_FluffyDream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_BlueFairy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Piledriver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_GrlzzlyTemple_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SunshineCloud_1</x:t>
-  </x:si>
-  <x:si>
     <x:t>Icon/Cocktail_GutPunch_1</x:t>
   </x:si>
   <x:si>
@@ -377,102 +473,6 @@
   </x:si>
   <x:si>
     <x:t>"이건 색이 아주 쓸데없이 갈색이야......."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TasteType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MakeRecipe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>자극적인 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>IconPath</x:t>
-  </x:si>
-  <x:si>
-    <x:t>캐릭터 고유 ID</x:t>
-  </x:si>
-  <x:si>
-    <x:t>거품 많은 드링크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FromType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MoodType</x:t>
-  </x:si>
-  <x:si>
-    <x:t>크레바스 스파이크</x:t>
-  </x:si>
-  <x:si>
-    <x:t>션샤인 클라우드</x:t>
-  </x:si>
-  <x:si>
-    <x:t>머큐리 블라스트</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_MoonBlast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BleedingJane_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SugarRush_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FrothyWater_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>"우리는 결국 포유류에 지나지 않는다네."</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BloomLight_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_PianoWoman_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Mercuryblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_ZenStar_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Beer_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Fail_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CreviceSpike_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Icon/Cocktail_Suplex_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_CobaltVelvet_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FringeWeaver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Brandtini_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_FluffyDream_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_BlueFairy_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Marsblast_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_Piledriver_1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Cocktail_SparkleStar_1</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -707,6 +707,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -789,6 +790,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -823,6 +825,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -867,6 +870,7 @@
           <x:font hs:extension="1">
             <x:color rgb="ffffffff"/>
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -910,6 +914,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:color rgb="ff000000"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -994,6 +999,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1014,6 +1020,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1044,6 +1051,7 @@
         <x:dxf hs:applyExtension="1">
           <x:font hs:extension="1">
             <x:b val="1"/>
+            <hs:useFontSpace val="0"/>
             <hs:size val="0"/>
             <hs:ratio val="0"/>
             <hs:spacing val="0"/>
@@ -1758,92 +1766,92 @@
   <x:sheetData>
     <x:row r="1" spans="1:4" ht="15.75" customHeight="1">
       <x:c r="A1" s="1" t="s">
-        <x:v>125</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="B1" s="1"/>
       <x:c r="C1" s="1" t="s">
-        <x:v>10</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>70</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="2" spans="1:8" ht="12.300000000000001">
       <x:c r="A2" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="B2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="D2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="F2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="G2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="H2" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>114</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:8" s="12" customFormat="1" ht="15.75" customHeight="1">
       <x:c r="A3" s="11" t="s">
-        <x:v>72</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B3" s="11" t="s">
-        <x:v>83</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C3" s="11" t="s">
-        <x:v>30</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D3" s="13" t="s">
-        <x:v>122</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="E3" s="13" t="s">
-        <x:v>121</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="F3" s="13" t="s">
-        <x:v>127</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="G3" s="13" t="s">
-        <x:v>128</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="H3" s="13" t="s">
-        <x:v>124</x:v>
+        <x:v>102</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A4" s="3" t="s">
-        <x:v>134</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="3" t="s">
-        <x:v>96</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C4" s="3" t="s">
-        <x:v>23</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D4" s="4" t="s">
-        <x:v>32</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E4" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F4" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G4" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H4" s="3" t="s">
-        <x:v>115</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="I4" s="4"/>
       <x:c r="J4" s="4"/>
@@ -1853,28 +1861,28 @@
     </x:row>
     <x:row r="5" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A5" s="3" t="s">
-        <x:v>152</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>94</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C5" s="5" t="s">
-        <x:v>61</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="D5" s="4" t="s">
-        <x:v>37</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E5" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F5" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G5" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H5" s="3" t="s">
-        <x:v>118</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="I5" s="4"/>
       <x:c r="J5" s="4"/>
@@ -1884,28 +1892,28 @@
     </x:row>
     <x:row r="6" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A6" s="5" t="s">
-        <x:v>149</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="B6" s="5" t="s">
-        <x:v>73</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C6" s="5" t="s">
-        <x:v>48</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>16</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F6" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G6" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H6" s="5" t="s">
-        <x:v>110</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="I6" s="4"/>
       <x:c r="K6" s="4"/>
@@ -1914,28 +1922,28 @@
     </x:row>
     <x:row r="7" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A7" s="6" t="s">
-        <x:v>147</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B7" s="3" t="s">
-        <x:v>95</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C7" s="3" t="s">
-        <x:v>41</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D7" s="4" t="s">
-        <x:v>34</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E7" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F7" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G7" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H7" s="6" t="s">
-        <x:v>117</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="I7" s="4"/>
       <x:c r="J7" s="4"/>
@@ -1945,28 +1953,28 @@
     </x:row>
     <x:row r="8" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A8" s="6" t="s">
-        <x:v>138</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="B8" s="3" t="s">
-        <x:v>85</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="C8" s="3" t="s">
-        <x:v>44</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D8" s="4" t="s">
-        <x:v>46</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="E8" s="4" t="s">
-        <x:v>88</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F8" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G8" s="4" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H8" s="6" t="s">
-        <x:v>107</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="I8" s="4"/>
       <x:c r="J8" s="4"/>
@@ -1976,28 +1984,28 @@
     </x:row>
     <x:row r="9" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A9" s="1" t="s">
-        <x:v>0</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="C9" s="3" t="s">
-        <x:v>39</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D9" s="4" t="s">
-        <x:v>20</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E9" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F9" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G9" s="4" t="s">
-        <x:v>62</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H9" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="I9" s="4"/>
       <x:c r="J9" s="4"/>
@@ -2007,28 +2015,28 @@
     </x:row>
     <x:row r="10" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A10" s="1" t="s">
-        <x:v>151</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D10" s="4" t="s">
-        <x:v>35</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E10" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F10" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G10" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H10" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="I10" s="4"/>
       <x:c r="J10" s="4"/>
@@ -2038,28 +2046,28 @@
     </x:row>
     <x:row r="11" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A11" s="6" t="s">
-        <x:v>4</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B11" s="6" t="s">
-        <x:v>101</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="D11" s="4" t="s">
-        <x:v>36</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="E11" s="4" t="s">
-        <x:v>91</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F11" s="4" t="s">
-        <x:v>75</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G11" s="4" t="s">
-        <x:v>63</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H11" s="6" t="s">
-        <x:v>144</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="I11" s="4"/>
       <x:c r="J11" s="4"/>
@@ -2069,28 +2077,28 @@
     </x:row>
     <x:row r="12" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A12" s="6" t="s">
-        <x:v>148</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B12" s="6" t="s">
-        <x:v>84</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C12" s="6" t="s">
-        <x:v>54</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D12" s="4" t="s">
-        <x:v>38</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="E12" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F12" s="4" t="s">
-        <x:v>74</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G12" s="4" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H12" s="6" t="s">
-        <x:v>108</x:v>
+        <x:v>138</x:v>
       </x:c>
       <x:c r="I12" s="4"/>
       <x:c r="J12" s="4"/>
@@ -2100,28 +2108,28 @@
     </x:row>
     <x:row r="13" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A13" s="6" t="s">
-        <x:v>2</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C13" s="3" t="s">
-        <x:v>136</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D13" s="4" t="s">
-        <x:v>14</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="E13" s="4" t="s">
-        <x:v>97</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F13" s="4" t="s">
-        <x:v>100</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G13" s="4" t="s">
-        <x:v>89</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="H13" s="6" t="s">
-        <x:v>106</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="I13" s="4"/>
       <x:c r="J13" s="4"/>
@@ -2131,28 +2139,28 @@
     </x:row>
     <x:row r="14" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A14" s="6" t="s">
-        <x:v>3</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="B14" s="7" t="s">
-        <x:v>66</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="D14" s="4" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="E14" s="4" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="F14" s="4" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="G14" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="H14" s="6" t="s">
         <x:v>7</x:v>
-      </x:c>
-      <x:c r="E14" s="4" t="s">
-        <x:v>97</x:v>
-      </x:c>
-      <x:c r="F14" s="4" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="G14" s="4" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="H14" s="6" t="s">
-        <x:v>140</x:v>
       </x:c>
       <x:c r="I14" s="4"/>
       <x:c r="J14" s="4"/>
@@ -2162,28 +2170,28 @@
     </x:row>
     <x:row r="15" spans="1:13" ht="15.75" customHeight="1">
       <x:c r="A15" s="6" t="s">
-        <x:v>137</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="D15" s="4" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="E15" s="4" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>120</x:v>
-      </x:c>
-      <x:c r="D15" s="4" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E15" s="4" t="s">
-        <x:v>123</x:v>
-      </x:c>
       <x:c r="F15" s="4" t="s">
-        <x:v>67</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G15" s="4" t="s">
-        <x:v>69</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H15" s="6" t="s">
-        <x:v>109</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="I15" s="4"/>
       <x:c r="J15" s="4"/>
@@ -2193,326 +2201,326 @@
     </x:row>
     <x:row r="16" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A16" s="6" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="B16" s="7" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="C16" s="7" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D16" s="2" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E16" s="2" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="F16" s="2" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="G16" s="2" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="H16" s="6" t="s">
         <x:v>9</x:v>
-      </x:c>
-      <x:c r="B16" s="7" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="C16" s="7" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D16" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="E16" s="2" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="F16" s="2" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G16" s="2" t="s">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="H16" s="6" t="s">
-        <x:v>141</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A17" s="6" t="s">
-        <x:v>135</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="B17" s="8" t="s">
-        <x:v>92</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C17" s="8" t="s">
-        <x:v>56</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D17" s="2" t="s">
-        <x:v>13</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="E17" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F17" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G17" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H17" s="6" t="s">
-        <x:v>104</x:v>
+        <x:v>136</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A18" s="6" t="s">
-        <x:v>145</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B18" s="8" t="s">
-        <x:v>82</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="C18" s="8" t="s">
-        <x:v>6</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D18" s="2" t="s">
-        <x:v>43</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E18" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F18" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G18" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H18" s="6" t="s">
-        <x:v>21</x:v>
+        <x:v>59</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A19" s="6" t="s">
-        <x:v>146</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B19" s="8" t="s">
-        <x:v>76</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="C19" s="8" t="s">
-        <x:v>5</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D19" s="2" t="s">
-        <x:v>52</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E19" s="2" t="s">
-        <x:v>126</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="F19" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G19" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H19" s="6" t="s">
-        <x:v>28</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A20" s="6" t="s">
-        <x:v>132</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="B20" s="8" t="s">
-        <x:v>79</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C20" s="8" t="s">
-        <x:v>58</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D20" s="2" t="s">
-        <x:v>53</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E20" s="2" t="s">
-        <x:v>88</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="F20" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G20" s="2" t="s">
-        <x:v>64</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="H20" s="6" t="s">
-        <x:v>105</x:v>
+        <x:v>139</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A21" s="6" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B21" s="8" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="B21" s="8" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="C21" s="7" t="s">
-        <x:v>50</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D21" s="2" t="s">
-        <x:v>19</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E21" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F21" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G21" s="2" t="s">
-        <x:v>69</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="H21" s="6" t="s">
-        <x:v>29</x:v>
+        <x:v>64</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A22" s="6" t="s">
-        <x:v>113</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="B22" s="8" t="s">
-        <x:v>130</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C22" s="8" t="s">
-        <x:v>18</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D22" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="E22" s="2" t="s">
-        <x:v>91</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="F22" s="2" t="s">
-        <x:v>74</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G22" s="2" t="s">
-        <x:v>90</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="H22" s="6" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A23" s="6" t="s">
-        <x:v>143</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="B23" s="8" t="s">
-        <x:v>129</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C23" s="8" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D23" s="2" t="s">
-        <x:v>40</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E23" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F23" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G23" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H23" s="6" t="s">
-        <x:v>27</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A24" s="6" t="s">
-        <x:v>139</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="B24" s="8" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="C24" s="8" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="D24" s="2" t="s">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="E24" s="2" t="s">
         <x:v>131</x:v>
       </x:c>
-      <x:c r="C24" s="8" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="D24" s="2" t="s">
-        <x:v>60</x:v>
-      </x:c>
-      <x:c r="E24" s="2" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="F24" s="2" t="s">
-        <x:v>100</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="G24" s="2" t="s">
-        <x:v>63</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="H24" s="6" t="s">
-        <x:v>22</x:v>
+        <x:v>58</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A25" s="6" t="s">
-        <x:v>1</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B25" s="8" t="s">
-        <x:v>86</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="C25" s="8" t="s">
-        <x:v>51</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D25" s="2" t="s">
-        <x:v>45</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E25" s="2" t="s">
-        <x:v>97</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="F25" s="2" t="s">
-        <x:v>67</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="G25" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H25" s="6" t="s">
-        <x:v>116</x:v>
+        <x:v>148</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A26" s="6" t="s">
-        <x:v>133</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="B26" s="9" t="s">
-        <x:v>93</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C26" s="9" t="s">
-        <x:v>49</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D26" s="2" t="s">
-        <x:v>33</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E26" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F26" s="2" t="s">
-        <x:v>68</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="G26" s="2" t="s">
-        <x:v>71</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="H26" s="6" t="s">
-        <x:v>24</x:v>
+        <x:v>60</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A27" s="6" t="s">
-        <x:v>150</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="B27" s="9" t="s">
-        <x:v>98</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="C27" s="9" t="s">
-        <x:v>26</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D27" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E27" s="2" t="s">
-        <x:v>123</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="F27" s="2" t="s">
-        <x:v>75</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="G27" s="2" t="s">
-        <x:v>62</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="H27" s="6" t="s">
-        <x:v>119</x:v>
+        <x:v>151</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:8" ht="15.75" customHeight="1">
       <x:c r="A28" s="14" t="s">
-        <x:v>8</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B28" s="9" t="s">
-        <x:v>103</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="C28" s="9"/>
       <x:c r="H28" s="2" t="s">
-        <x:v>142</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:3" ht="15.75" customHeight="1">
